--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -79,24 +79,12 @@
     <t xml:space="preserve">Lago Verde</t>
   </si>
   <si>
-    <t xml:space="preserve">11101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coyhaique</t>
-  </si>
-  <si>
     <t xml:space="preserve">11301</t>
   </si>
   <si>
     <t xml:space="preserve">Cochrane</t>
   </si>
   <si>
-    <t xml:space="preserve">11201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
@@ -982,6 +970,12 @@
     <t xml:space="preserve">San Ignacio</t>
   </si>
   <si>
+    <t xml:space="preserve">6204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Marchihue</t>
+  </si>
+  <si>
     <t xml:space="preserve">16104</t>
   </si>
   <si>
@@ -1336,6 +1330,12 @@
     <t xml:space="preserve">Combarbalá</t>
   </si>
   <si>
+    <t xml:space="preserve">4105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paiguano</t>
+  </si>
+  <si>
     <t xml:space="preserve">4106</t>
   </si>
   <si>
@@ -2104,7 +2104,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-08 10:18</t>
+    <t xml:space="preserve">2026-09-09 20:00</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2680,7 +2680,7 @@
         <v>15</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>79.96</v>
+        <v>79.53</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>15</v>
@@ -2691,16 +2691,16 @@
         <v>2020</v>
       </c>
       <c r="B6" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>13</v>
@@ -2712,7 +2712,7 @@
         <v>15</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>79.53</v>
+        <v>78.75</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>15</v>
@@ -2723,16 +2723,16 @@
         <v>2020</v>
       </c>
       <c r="B7" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2744,7 +2744,7 @@
         <v>15</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>79.49</v>
+        <v>78.72</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>15</v>
@@ -2755,10 +2755,10 @@
         <v>2020</v>
       </c>
       <c r="B8" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>27</v>
@@ -2776,7 +2776,7 @@
         <v>15</v>
       </c>
       <c r="I8" s="2" t="n">
-        <v>78.75</v>
+        <v>77.95</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>15</v>
@@ -2787,10 +2787,10 @@
         <v>2020</v>
       </c>
       <c r="B9" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D9" s="2" t="s">
         <v>29</v>
@@ -2808,7 +2808,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>78.72</v>
+        <v>77.67</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>15</v>
@@ -2819,10 +2819,10 @@
         <v>2020</v>
       </c>
       <c r="B10" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>31</v>
@@ -2840,7 +2840,7 @@
         <v>15</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>77.95</v>
+        <v>77.13</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>15</v>
@@ -2872,7 +2872,7 @@
         <v>15</v>
       </c>
       <c r="I11" s="2" t="n">
-        <v>77.67</v>
+        <v>76.7</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>15</v>
@@ -2883,10 +2883,10 @@
         <v>2020</v>
       </c>
       <c r="B12" s="2" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="D12" s="2" t="s">
         <v>35</v>
@@ -2904,7 +2904,7 @@
         <v>15</v>
       </c>
       <c r="I12" s="2" t="n">
-        <v>77.13</v>
+        <v>75.92</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>15</v>
@@ -2915,10 +2915,10 @@
         <v>2020</v>
       </c>
       <c r="B13" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>37</v>
@@ -2936,7 +2936,7 @@
         <v>15</v>
       </c>
       <c r="I13" s="2" t="n">
-        <v>76.7</v>
+        <v>75.41</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>15</v>
@@ -2947,10 +2947,10 @@
         <v>2020</v>
       </c>
       <c r="B14" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>39</v>
@@ -2968,7 +2968,7 @@
         <v>15</v>
       </c>
       <c r="I14" s="2" t="n">
-        <v>75.92</v>
+        <v>74</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>15</v>
@@ -2982,7 +2982,7 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>41</v>
@@ -3000,7 +3000,7 @@
         <v>15</v>
       </c>
       <c r="I15" s="2" t="n">
-        <v>75.41</v>
+        <v>71.77</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>15</v>
@@ -3014,7 +3014,7 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>43</v>
@@ -3032,7 +3032,7 @@
         <v>15</v>
       </c>
       <c r="I16" s="2" t="n">
-        <v>74</v>
+        <v>68.18</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>15</v>
@@ -3043,28 +3043,28 @@
         <v>2020</v>
       </c>
       <c r="B17" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I17" s="2" t="n">
-        <v>71.77</v>
+        <v>87.68</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>15</v>
@@ -3075,28 +3075,28 @@
         <v>2020</v>
       </c>
       <c r="B18" s="2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>26</v>
+        <v>45</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>13</v>
+        <v>48</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>14</v>
+        <v>49</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I18" s="2" t="n">
-        <v>68.18</v>
+        <v>84.85</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>15</v>
@@ -3107,28 +3107,28 @@
         <v>2020</v>
       </c>
       <c r="B19" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I19" s="2" t="n">
-        <v>87.68</v>
+        <v>81.49</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>15</v>
@@ -3139,28 +3139,28 @@
         <v>2020</v>
       </c>
       <c r="B20" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I20" s="2" t="n">
-        <v>84.85</v>
+        <v>79.81</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>15</v>
@@ -3171,28 +3171,28 @@
         <v>2020</v>
       </c>
       <c r="B21" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I21" s="2" t="n">
-        <v>81.49</v>
+        <v>79.56</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>15</v>
@@ -3206,7 +3206,7 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>60</v>
@@ -3215,16 +3215,16 @@
         <v>61</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I22" s="2" t="n">
-        <v>79.81</v>
+        <v>79.42</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>15</v>
@@ -3238,7 +3238,7 @@
         <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>62</v>
@@ -3247,16 +3247,16 @@
         <v>63</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I23" s="2" t="n">
-        <v>79.56</v>
+        <v>79.03</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>15</v>
@@ -3270,7 +3270,7 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>64</v>
@@ -3279,16 +3279,16 @@
         <v>65</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I24" s="2" t="n">
-        <v>79.42</v>
+        <v>79</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>15</v>
@@ -3299,28 +3299,28 @@
         <v>2020</v>
       </c>
       <c r="B25" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I25" s="2" t="n">
-        <v>79.03</v>
+        <v>78.89</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>15</v>
@@ -3331,28 +3331,28 @@
         <v>2020</v>
       </c>
       <c r="B26" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I26" s="2" t="n">
-        <v>79</v>
+        <v>78.42</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>15</v>
@@ -3363,28 +3363,28 @@
         <v>2020</v>
       </c>
       <c r="B27" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I27" s="2" t="n">
-        <v>78.89</v>
+        <v>78.14</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>15</v>
@@ -3395,28 +3395,28 @@
         <v>2020</v>
       </c>
       <c r="B28" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I28" s="2" t="n">
-        <v>78.42</v>
+        <v>77.94</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>15</v>
@@ -3427,10 +3427,10 @@
         <v>2020</v>
       </c>
       <c r="B29" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>76</v>
@@ -3439,16 +3439,16 @@
         <v>77</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I29" s="2" t="n">
-        <v>78.14</v>
+        <v>77.92</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>15</v>
@@ -3459,10 +3459,10 @@
         <v>2020</v>
       </c>
       <c r="B30" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>78</v>
@@ -3471,16 +3471,16 @@
         <v>79</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I30" s="2" t="n">
-        <v>77.94</v>
+        <v>77.68</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>15</v>
@@ -3491,10 +3491,10 @@
         <v>2020</v>
       </c>
       <c r="B31" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>80</v>
@@ -3503,16 +3503,16 @@
         <v>81</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I31" s="2" t="n">
-        <v>77.92</v>
+        <v>77.57</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>15</v>
@@ -3526,7 +3526,7 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>82</v>
@@ -3535,16 +3535,16 @@
         <v>83</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I32" s="2" t="n">
-        <v>77.68</v>
+        <v>77.33</v>
       </c>
       <c r="J32" s="2" t="s">
         <v>15</v>
@@ -3555,10 +3555,10 @@
         <v>2020</v>
       </c>
       <c r="B33" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>84</v>
@@ -3567,16 +3567,16 @@
         <v>85</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I33" s="2" t="n">
-        <v>77.57</v>
+        <v>77.31</v>
       </c>
       <c r="J33" s="2" t="s">
         <v>15</v>
@@ -3587,10 +3587,10 @@
         <v>2020</v>
       </c>
       <c r="B34" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>86</v>
@@ -3599,16 +3599,16 @@
         <v>87</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I34" s="2" t="n">
-        <v>77.33</v>
+        <v>77.05</v>
       </c>
       <c r="J34" s="2" t="s">
         <v>15</v>
@@ -3622,7 +3622,7 @@
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>88</v>
@@ -3631,16 +3631,16 @@
         <v>89</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I35" s="2" t="n">
-        <v>77.31</v>
+        <v>76.94</v>
       </c>
       <c r="J35" s="2" t="s">
         <v>15</v>
@@ -3654,7 +3654,7 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D36" s="2" t="s">
         <v>90</v>
@@ -3663,16 +3663,16 @@
         <v>91</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I36" s="2" t="n">
-        <v>77.05</v>
+        <v>76.84</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>15</v>
@@ -3683,10 +3683,10 @@
         <v>2020</v>
       </c>
       <c r="B37" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D37" s="2" t="s">
         <v>92</v>
@@ -3695,16 +3695,16 @@
         <v>93</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I37" s="2" t="n">
-        <v>76.94</v>
+        <v>76.81</v>
       </c>
       <c r="J37" s="2" t="s">
         <v>15</v>
@@ -3715,10 +3715,10 @@
         <v>2020</v>
       </c>
       <c r="B38" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>94</v>
@@ -3727,16 +3727,16 @@
         <v>95</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I38" s="2" t="n">
-        <v>76.84</v>
+        <v>76.7</v>
       </c>
       <c r="J38" s="2" t="s">
         <v>15</v>
@@ -3747,10 +3747,10 @@
         <v>2020</v>
       </c>
       <c r="B39" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>96</v>
@@ -3759,16 +3759,16 @@
         <v>97</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I39" s="2" t="n">
-        <v>76.81</v>
+        <v>76.64</v>
       </c>
       <c r="J39" s="2" t="s">
         <v>15</v>
@@ -3779,10 +3779,10 @@
         <v>2020</v>
       </c>
       <c r="B40" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>98</v>
@@ -3791,16 +3791,16 @@
         <v>99</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I40" s="2" t="n">
-        <v>76.7</v>
+        <v>76.57</v>
       </c>
       <c r="J40" s="2" t="s">
         <v>15</v>
@@ -3811,10 +3811,10 @@
         <v>2020</v>
       </c>
       <c r="B41" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>100</v>
@@ -3823,16 +3823,16 @@
         <v>101</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I41" s="2" t="n">
-        <v>76.64</v>
+        <v>76.44</v>
       </c>
       <c r="J41" s="2" t="s">
         <v>15</v>
@@ -3846,7 +3846,7 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>102</v>
@@ -3855,16 +3855,16 @@
         <v>103</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I42" s="2" t="n">
-        <v>76.57</v>
+        <v>76.32</v>
       </c>
       <c r="J42" s="2" t="s">
         <v>15</v>
@@ -3875,10 +3875,10 @@
         <v>2020</v>
       </c>
       <c r="B43" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>104</v>
@@ -3887,16 +3887,16 @@
         <v>105</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I43" s="2" t="n">
-        <v>76.44</v>
+        <v>76.29</v>
       </c>
       <c r="J43" s="2" t="s">
         <v>15</v>
@@ -3907,10 +3907,10 @@
         <v>2020</v>
       </c>
       <c r="B44" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>106</v>
@@ -3919,16 +3919,16 @@
         <v>107</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I44" s="2" t="n">
-        <v>76.32</v>
+        <v>76.28</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>15</v>
@@ -3942,7 +3942,7 @@
         <v>6</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D45" s="2" t="s">
         <v>108</v>
@@ -3951,16 +3951,16 @@
         <v>109</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I45" s="2" t="n">
-        <v>76.29</v>
+        <v>76.27</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>15</v>
@@ -3974,25 +3974,25 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D46" s="2" t="s">
         <v>110</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>111</v>
+        <v>66</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I46" s="2" t="n">
-        <v>76.28</v>
+        <v>76.26</v>
       </c>
       <c r="J46" s="2" t="s">
         <v>15</v>
@@ -4003,28 +4003,28 @@
         <v>2020</v>
       </c>
       <c r="B47" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>113</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I47" s="2" t="n">
-        <v>76.27</v>
+        <v>76.2</v>
       </c>
       <c r="J47" s="2" t="s">
         <v>15</v>
@@ -4035,28 +4035,28 @@
         <v>2020</v>
       </c>
       <c r="B48" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D48" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E48" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E48" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I48" s="2" t="n">
-        <v>76.26</v>
+        <v>76.17</v>
       </c>
       <c r="J48" s="2" t="s">
         <v>15</v>
@@ -4067,10 +4067,10 @@
         <v>2020</v>
       </c>
       <c r="B49" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>115</v>
@@ -4079,16 +4079,16 @@
         <v>116</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I49" s="2" t="n">
-        <v>76.2</v>
+        <v>76.03</v>
       </c>
       <c r="J49" s="2" t="s">
         <v>15</v>
@@ -4099,10 +4099,10 @@
         <v>2020</v>
       </c>
       <c r="B50" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>117</v>
@@ -4111,16 +4111,16 @@
         <v>118</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I50" s="2" t="n">
-        <v>76.17</v>
+        <v>75.98</v>
       </c>
       <c r="J50" s="2" t="s">
         <v>15</v>
@@ -4134,7 +4134,7 @@
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>119</v>
@@ -4143,16 +4143,16 @@
         <v>120</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I51" s="2" t="n">
-        <v>76.03</v>
+        <v>75.97</v>
       </c>
       <c r="J51" s="2" t="s">
         <v>15</v>
@@ -4163,10 +4163,10 @@
         <v>2020</v>
       </c>
       <c r="B52" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>121</v>
@@ -4175,16 +4175,16 @@
         <v>122</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I52" s="2" t="n">
-        <v>75.98</v>
+        <v>75.89</v>
       </c>
       <c r="J52" s="2" t="s">
         <v>15</v>
@@ -4195,10 +4195,10 @@
         <v>2020</v>
       </c>
       <c r="B53" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>123</v>
@@ -4207,16 +4207,16 @@
         <v>124</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I53" s="2" t="n">
-        <v>75.97</v>
+        <v>75.65</v>
       </c>
       <c r="J53" s="2" t="s">
         <v>15</v>
@@ -4227,10 +4227,10 @@
         <v>2020</v>
       </c>
       <c r="B54" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>125</v>
@@ -4239,16 +4239,16 @@
         <v>126</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I54" s="2" t="n">
-        <v>75.89</v>
+        <v>75.58</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>15</v>
@@ -4259,10 +4259,10 @@
         <v>2020</v>
       </c>
       <c r="B55" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>127</v>
@@ -4271,16 +4271,16 @@
         <v>128</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I55" s="2" t="n">
-        <v>75.65</v>
+        <v>75.52</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>15</v>
@@ -4291,10 +4291,10 @@
         <v>2020</v>
       </c>
       <c r="B56" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>129</v>
@@ -4303,16 +4303,16 @@
         <v>130</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I56" s="2" t="n">
-        <v>75.58</v>
+        <v>75.51</v>
       </c>
       <c r="J56" s="2" t="s">
         <v>15</v>
@@ -4323,10 +4323,10 @@
         <v>2020</v>
       </c>
       <c r="B57" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>131</v>
@@ -4335,16 +4335,16 @@
         <v>132</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I57" s="2" t="n">
-        <v>75.52</v>
+        <v>75.49</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>15</v>
@@ -4355,10 +4355,10 @@
         <v>2020</v>
       </c>
       <c r="B58" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D58" s="2" t="s">
         <v>133</v>
@@ -4367,16 +4367,16 @@
         <v>134</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I58" s="2" t="n">
-        <v>75.51</v>
+        <v>75.48</v>
       </c>
       <c r="J58" s="2" t="s">
         <v>15</v>
@@ -4387,10 +4387,10 @@
         <v>2020</v>
       </c>
       <c r="B59" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>135</v>
@@ -4399,16 +4399,16 @@
         <v>136</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I59" s="2" t="n">
-        <v>75.49</v>
+        <v>75.47</v>
       </c>
       <c r="J59" s="2" t="s">
         <v>15</v>
@@ -4419,10 +4419,10 @@
         <v>2020</v>
       </c>
       <c r="B60" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>137</v>
@@ -4431,16 +4431,16 @@
         <v>138</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I60" s="2" t="n">
-        <v>75.48</v>
+        <v>75.47</v>
       </c>
       <c r="J60" s="2" t="s">
         <v>15</v>
@@ -4454,7 +4454,7 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>139</v>
@@ -4463,16 +4463,16 @@
         <v>140</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I61" s="2" t="n">
-        <v>75.47</v>
+        <v>75.46</v>
       </c>
       <c r="J61" s="2" t="s">
         <v>15</v>
@@ -4483,10 +4483,10 @@
         <v>2020</v>
       </c>
       <c r="B62" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>141</v>
@@ -4495,16 +4495,16 @@
         <v>142</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I62" s="2" t="n">
-        <v>75.47</v>
+        <v>75.41</v>
       </c>
       <c r="J62" s="2" t="s">
         <v>15</v>
@@ -4518,7 +4518,7 @@
         <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>143</v>
@@ -4527,16 +4527,16 @@
         <v>144</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I63" s="2" t="n">
-        <v>75.46</v>
+        <v>75.39</v>
       </c>
       <c r="J63" s="2" t="s">
         <v>15</v>
@@ -4547,10 +4547,10 @@
         <v>2020</v>
       </c>
       <c r="B64" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>145</v>
@@ -4559,16 +4559,16 @@
         <v>146</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I64" s="2" t="n">
-        <v>75.41</v>
+        <v>75.39</v>
       </c>
       <c r="J64" s="2" t="s">
         <v>15</v>
@@ -4579,10 +4579,10 @@
         <v>2020</v>
       </c>
       <c r="B65" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>147</v>
@@ -4591,16 +4591,16 @@
         <v>148</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I65" s="2" t="n">
-        <v>75.39</v>
+        <v>75.36</v>
       </c>
       <c r="J65" s="2" t="s">
         <v>15</v>
@@ -4611,10 +4611,10 @@
         <v>2020</v>
       </c>
       <c r="B66" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>149</v>
@@ -4623,16 +4623,16 @@
         <v>150</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I66" s="2" t="n">
-        <v>75.39</v>
+        <v>75.27</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>15</v>
@@ -4643,10 +4643,10 @@
         <v>2020</v>
       </c>
       <c r="B67" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>151</v>
@@ -4655,16 +4655,16 @@
         <v>152</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I67" s="2" t="n">
-        <v>75.36</v>
+        <v>75.23</v>
       </c>
       <c r="J67" s="2" t="s">
         <v>15</v>
@@ -4675,10 +4675,10 @@
         <v>2020</v>
       </c>
       <c r="B68" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>153</v>
@@ -4687,16 +4687,16 @@
         <v>154</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I68" s="2" t="n">
-        <v>75.27</v>
+        <v>75.2</v>
       </c>
       <c r="J68" s="2" t="s">
         <v>15</v>
@@ -4707,10 +4707,10 @@
         <v>2020</v>
       </c>
       <c r="B69" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D69" s="2" t="s">
         <v>155</v>
@@ -4719,16 +4719,16 @@
         <v>156</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I69" s="2" t="n">
-        <v>75.23</v>
+        <v>75.19</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>15</v>
@@ -4739,10 +4739,10 @@
         <v>2020</v>
       </c>
       <c r="B70" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>157</v>
@@ -4751,16 +4751,16 @@
         <v>158</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I70" s="2" t="n">
-        <v>75.2</v>
+        <v>75.16</v>
       </c>
       <c r="J70" s="2" t="s">
         <v>15</v>
@@ -4774,7 +4774,7 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>159</v>
@@ -4783,16 +4783,16 @@
         <v>160</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I71" s="2" t="n">
-        <v>75.19</v>
+        <v>75.1</v>
       </c>
       <c r="J71" s="2" t="s">
         <v>15</v>
@@ -4803,10 +4803,10 @@
         <v>2020</v>
       </c>
       <c r="B72" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>161</v>
@@ -4815,16 +4815,16 @@
         <v>162</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I72" s="2" t="n">
-        <v>75.16</v>
+        <v>74.99</v>
       </c>
       <c r="J72" s="2" t="s">
         <v>15</v>
@@ -4838,7 +4838,7 @@
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>163</v>
@@ -4847,16 +4847,16 @@
         <v>164</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I73" s="2" t="n">
-        <v>75.1</v>
+        <v>74.97</v>
       </c>
       <c r="J73" s="2" t="s">
         <v>15</v>
@@ -4867,10 +4867,10 @@
         <v>2020</v>
       </c>
       <c r="B74" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>165</v>
@@ -4879,16 +4879,16 @@
         <v>166</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I74" s="2" t="n">
-        <v>74.99</v>
+        <v>74.97</v>
       </c>
       <c r="J74" s="2" t="s">
         <v>15</v>
@@ -4899,10 +4899,10 @@
         <v>2020</v>
       </c>
       <c r="B75" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D75" s="2" t="s">
         <v>167</v>
@@ -4911,16 +4911,16 @@
         <v>168</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I75" s="2" t="n">
-        <v>74.97</v>
+        <v>74.95</v>
       </c>
       <c r="J75" s="2" t="s">
         <v>15</v>
@@ -4931,10 +4931,10 @@
         <v>2020</v>
       </c>
       <c r="B76" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>169</v>
@@ -4943,16 +4943,16 @@
         <v>170</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I76" s="2" t="n">
-        <v>74.97</v>
+        <v>74.89</v>
       </c>
       <c r="J76" s="2" t="s">
         <v>15</v>
@@ -4963,10 +4963,10 @@
         <v>2020</v>
       </c>
       <c r="B77" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>171</v>
@@ -4975,16 +4975,16 @@
         <v>172</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I77" s="2" t="n">
-        <v>74.95</v>
+        <v>74.88</v>
       </c>
       <c r="J77" s="2" t="s">
         <v>15</v>
@@ -4995,10 +4995,10 @@
         <v>2020</v>
       </c>
       <c r="B78" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>173</v>
@@ -5007,16 +5007,16 @@
         <v>174</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I78" s="2" t="n">
-        <v>74.89</v>
+        <v>74.85</v>
       </c>
       <c r="J78" s="2" t="s">
         <v>15</v>
@@ -5027,10 +5027,10 @@
         <v>2020</v>
       </c>
       <c r="B79" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>175</v>
@@ -5039,16 +5039,16 @@
         <v>176</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I79" s="2" t="n">
-        <v>74.88</v>
+        <v>74.79</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>15</v>
@@ -5059,10 +5059,10 @@
         <v>2020</v>
       </c>
       <c r="B80" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>177</v>
@@ -5071,16 +5071,16 @@
         <v>178</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I80" s="2" t="n">
-        <v>74.85</v>
+        <v>74.77</v>
       </c>
       <c r="J80" s="2" t="s">
         <v>15</v>
@@ -5091,10 +5091,10 @@
         <v>2020</v>
       </c>
       <c r="B81" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D81" s="2" t="s">
         <v>179</v>
@@ -5103,16 +5103,16 @@
         <v>180</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I81" s="2" t="n">
-        <v>74.79</v>
+        <v>74.74</v>
       </c>
       <c r="J81" s="2" t="s">
         <v>15</v>
@@ -5123,10 +5123,10 @@
         <v>2020</v>
       </c>
       <c r="B82" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>181</v>
@@ -5135,16 +5135,16 @@
         <v>182</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I82" s="2" t="n">
-        <v>74.77</v>
+        <v>74.72</v>
       </c>
       <c r="J82" s="2" t="s">
         <v>15</v>
@@ -5155,10 +5155,10 @@
         <v>2020</v>
       </c>
       <c r="B83" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>183</v>
@@ -5167,16 +5167,16 @@
         <v>184</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I83" s="2" t="n">
-        <v>74.74</v>
+        <v>74.69</v>
       </c>
       <c r="J83" s="2" t="s">
         <v>15</v>
@@ -5187,10 +5187,10 @@
         <v>2020</v>
       </c>
       <c r="B84" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>185</v>
@@ -5199,16 +5199,16 @@
         <v>186</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I84" s="2" t="n">
-        <v>74.72</v>
+        <v>74.68</v>
       </c>
       <c r="J84" s="2" t="s">
         <v>15</v>
@@ -5219,10 +5219,10 @@
         <v>2020</v>
       </c>
       <c r="B85" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>187</v>
@@ -5231,16 +5231,16 @@
         <v>188</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I85" s="2" t="n">
-        <v>74.69</v>
+        <v>74.66</v>
       </c>
       <c r="J85" s="2" t="s">
         <v>15</v>
@@ -5251,10 +5251,10 @@
         <v>2020</v>
       </c>
       <c r="B86" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>189</v>
@@ -5263,16 +5263,16 @@
         <v>190</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I86" s="2" t="n">
-        <v>74.68</v>
+        <v>74.65</v>
       </c>
       <c r="J86" s="2" t="s">
         <v>15</v>
@@ -5286,7 +5286,7 @@
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>191</v>
@@ -5295,16 +5295,16 @@
         <v>192</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I87" s="2" t="n">
-        <v>74.66</v>
+        <v>74.61</v>
       </c>
       <c r="J87" s="2" t="s">
         <v>15</v>
@@ -5315,10 +5315,10 @@
         <v>2020</v>
       </c>
       <c r="B88" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>193</v>
@@ -5327,16 +5327,16 @@
         <v>194</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I88" s="2" t="n">
-        <v>74.65</v>
+        <v>74.59</v>
       </c>
       <c r="J88" s="2" t="s">
         <v>15</v>
@@ -5347,10 +5347,10 @@
         <v>2020</v>
       </c>
       <c r="B89" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>195</v>
@@ -5359,16 +5359,16 @@
         <v>196</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I89" s="2" t="n">
-        <v>74.61</v>
+        <v>74.51</v>
       </c>
       <c r="J89" s="2" t="s">
         <v>15</v>
@@ -5379,10 +5379,10 @@
         <v>2020</v>
       </c>
       <c r="B90" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>197</v>
@@ -5391,16 +5391,16 @@
         <v>198</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I90" s="2" t="n">
-        <v>74.59</v>
+        <v>74.47</v>
       </c>
       <c r="J90" s="2" t="s">
         <v>15</v>
@@ -5411,10 +5411,10 @@
         <v>2020</v>
       </c>
       <c r="B91" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>199</v>
@@ -5423,16 +5423,16 @@
         <v>200</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I91" s="2" t="n">
-        <v>74.51</v>
+        <v>74.45</v>
       </c>
       <c r="J91" s="2" t="s">
         <v>15</v>
@@ -5446,7 +5446,7 @@
         <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>201</v>
@@ -5455,16 +5455,16 @@
         <v>202</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I92" s="2" t="n">
-        <v>74.47</v>
+        <v>74.35</v>
       </c>
       <c r="J92" s="2" t="s">
         <v>15</v>
@@ -5475,10 +5475,10 @@
         <v>2020</v>
       </c>
       <c r="B93" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D93" s="2" t="s">
         <v>203</v>
@@ -5487,16 +5487,16 @@
         <v>204</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I93" s="2" t="n">
-        <v>74.45</v>
+        <v>74.35</v>
       </c>
       <c r="J93" s="2" t="s">
         <v>15</v>
@@ -5507,10 +5507,10 @@
         <v>2020</v>
       </c>
       <c r="B94" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D94" s="2" t="s">
         <v>205</v>
@@ -5519,10 +5519,10 @@
         <v>206</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5542,7 +5542,7 @@
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="D95" s="2" t="s">
         <v>207</v>
@@ -5551,16 +5551,16 @@
         <v>208</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I95" s="2" t="n">
-        <v>74.35</v>
+        <v>74.34</v>
       </c>
       <c r="J95" s="2" t="s">
         <v>15</v>
@@ -5571,10 +5571,10 @@
         <v>2020</v>
       </c>
       <c r="B96" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D96" s="2" t="s">
         <v>209</v>
@@ -5583,16 +5583,16 @@
         <v>210</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I96" s="2" t="n">
-        <v>74.35</v>
+        <v>74.3</v>
       </c>
       <c r="J96" s="2" t="s">
         <v>15</v>
@@ -5603,10 +5603,10 @@
         <v>2020</v>
       </c>
       <c r="B97" s="2" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D97" s="2" t="s">
         <v>211</v>
@@ -5615,16 +5615,16 @@
         <v>212</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I97" s="2" t="n">
-        <v>74.34</v>
+        <v>74.29</v>
       </c>
       <c r="J97" s="2" t="s">
         <v>15</v>
@@ -5635,10 +5635,10 @@
         <v>2020</v>
       </c>
       <c r="B98" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D98" s="2" t="s">
         <v>213</v>
@@ -5647,16 +5647,16 @@
         <v>214</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I98" s="2" t="n">
-        <v>74.3</v>
+        <v>74.26</v>
       </c>
       <c r="J98" s="2" t="s">
         <v>15</v>
@@ -5667,10 +5667,10 @@
         <v>2020</v>
       </c>
       <c r="B99" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D99" s="2" t="s">
         <v>215</v>
@@ -5679,16 +5679,16 @@
         <v>216</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I99" s="2" t="n">
-        <v>74.29</v>
+        <v>74.22</v>
       </c>
       <c r="J99" s="2" t="s">
         <v>15</v>
@@ -5699,10 +5699,10 @@
         <v>2020</v>
       </c>
       <c r="B100" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D100" s="2" t="s">
         <v>217</v>
@@ -5711,16 +5711,16 @@
         <v>218</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I100" s="2" t="n">
-        <v>74.26</v>
+        <v>74.22</v>
       </c>
       <c r="J100" s="2" t="s">
         <v>15</v>
@@ -5731,10 +5731,10 @@
         <v>2020</v>
       </c>
       <c r="B101" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D101" s="2" t="s">
         <v>219</v>
@@ -5743,16 +5743,16 @@
         <v>220</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I101" s="2" t="n">
-        <v>74.22</v>
+        <v>74.18</v>
       </c>
       <c r="J101" s="2" t="s">
         <v>15</v>
@@ -5766,7 +5766,7 @@
         <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D102" s="2" t="s">
         <v>221</v>
@@ -5775,16 +5775,16 @@
         <v>222</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I102" s="2" t="n">
-        <v>74.22</v>
+        <v>74.17</v>
       </c>
       <c r="J102" s="2" t="s">
         <v>15</v>
@@ -5798,7 +5798,7 @@
         <v>6</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D103" s="2" t="s">
         <v>223</v>
@@ -5807,16 +5807,16 @@
         <v>224</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I103" s="2" t="n">
-        <v>74.18</v>
+        <v>74.16</v>
       </c>
       <c r="J103" s="2" t="s">
         <v>15</v>
@@ -5827,10 +5827,10 @@
         <v>2020</v>
       </c>
       <c r="B104" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>225</v>
@@ -5839,16 +5839,16 @@
         <v>226</v>
       </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I104" s="2" t="n">
-        <v>74.17</v>
+        <v>74.14</v>
       </c>
       <c r="J104" s="2" t="s">
         <v>15</v>
@@ -5859,10 +5859,10 @@
         <v>2020</v>
       </c>
       <c r="B105" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>227</v>
@@ -5871,16 +5871,16 @@
         <v>228</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I105" s="2" t="n">
-        <v>74.16</v>
+        <v>74.1</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>15</v>
@@ -5891,10 +5891,10 @@
         <v>2020</v>
       </c>
       <c r="B106" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D106" s="2" t="s">
         <v>229</v>
@@ -5903,16 +5903,16 @@
         <v>230</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>74.14</v>
+        <v>74.07</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5923,10 +5923,10 @@
         <v>2020</v>
       </c>
       <c r="B107" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D107" s="2" t="s">
         <v>231</v>
@@ -5935,16 +5935,16 @@
         <v>232</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I107" s="2" t="n">
-        <v>74.1</v>
+        <v>74.04</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>15</v>
@@ -5955,10 +5955,10 @@
         <v>2020</v>
       </c>
       <c r="B108" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D108" s="2" t="s">
         <v>233</v>
@@ -5967,16 +5967,16 @@
         <v>234</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I108" s="2" t="n">
-        <v>74.07</v>
+        <v>74.03</v>
       </c>
       <c r="J108" s="2" t="s">
         <v>15</v>
@@ -5987,10 +5987,10 @@
         <v>2020</v>
       </c>
       <c r="B109" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D109" s="2" t="s">
         <v>235</v>
@@ -5999,16 +5999,16 @@
         <v>236</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I109" s="2" t="n">
-        <v>74.04</v>
+        <v>73.95</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>15</v>
@@ -6019,10 +6019,10 @@
         <v>2020</v>
       </c>
       <c r="B110" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D110" s="2" t="s">
         <v>237</v>
@@ -6031,16 +6031,16 @@
         <v>238</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I110" s="2" t="n">
-        <v>74.03</v>
+        <v>73.89</v>
       </c>
       <c r="J110" s="2" t="s">
         <v>15</v>
@@ -6051,10 +6051,10 @@
         <v>2020</v>
       </c>
       <c r="B111" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D111" s="2" t="s">
         <v>239</v>
@@ -6063,16 +6063,16 @@
         <v>240</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I111" s="2" t="n">
-        <v>73.95</v>
+        <v>73.88</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>15</v>
@@ -6083,10 +6083,10 @@
         <v>2020</v>
       </c>
       <c r="B112" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>241</v>
@@ -6095,16 +6095,16 @@
         <v>242</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I112" s="2" t="n">
-        <v>73.89</v>
+        <v>73.87</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>15</v>
@@ -6115,10 +6115,10 @@
         <v>2020</v>
       </c>
       <c r="B113" s="2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="D113" s="2" t="s">
         <v>243</v>
@@ -6127,16 +6127,16 @@
         <v>244</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I113" s="2" t="n">
-        <v>73.88</v>
+        <v>73.78</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>15</v>
@@ -6147,10 +6147,10 @@
         <v>2020</v>
       </c>
       <c r="B114" s="2" t="n">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>59</v>
+        <v>71</v>
       </c>
       <c r="D114" s="2" t="s">
         <v>245</v>
@@ -6159,16 +6159,16 @@
         <v>246</v>
       </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I114" s="2" t="n">
-        <v>73.87</v>
+        <v>73.76</v>
       </c>
       <c r="J114" s="2" t="s">
         <v>15</v>
@@ -6179,10 +6179,10 @@
         <v>2020</v>
       </c>
       <c r="B115" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D115" s="2" t="s">
         <v>247</v>
@@ -6191,16 +6191,16 @@
         <v>248</v>
       </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I115" s="2" t="n">
-        <v>73.78</v>
+        <v>73.71</v>
       </c>
       <c r="J115" s="2" t="s">
         <v>15</v>
@@ -6214,7 +6214,7 @@
         <v>16</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D116" s="2" t="s">
         <v>249</v>
@@ -6223,16 +6223,16 @@
         <v>250</v>
       </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I116" s="2" t="n">
-        <v>73.76</v>
+        <v>73.65</v>
       </c>
       <c r="J116" s="2" t="s">
         <v>15</v>
@@ -6243,10 +6243,10 @@
         <v>2020</v>
       </c>
       <c r="B117" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D117" s="2" t="s">
         <v>251</v>
@@ -6255,16 +6255,16 @@
         <v>252</v>
       </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I117" s="2" t="n">
-        <v>73.71</v>
+        <v>73.57</v>
       </c>
       <c r="J117" s="2" t="s">
         <v>15</v>
@@ -6275,10 +6275,10 @@
         <v>2020</v>
       </c>
       <c r="B118" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D118" s="2" t="s">
         <v>253</v>
@@ -6287,16 +6287,16 @@
         <v>254</v>
       </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I118" s="2" t="n">
-        <v>73.65</v>
+        <v>73.53</v>
       </c>
       <c r="J118" s="2" t="s">
         <v>15</v>
@@ -6307,10 +6307,10 @@
         <v>2020</v>
       </c>
       <c r="B119" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D119" s="2" t="s">
         <v>255</v>
@@ -6319,16 +6319,16 @@
         <v>256</v>
       </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I119" s="2" t="n">
-        <v>73.57</v>
+        <v>73.48</v>
       </c>
       <c r="J119" s="2" t="s">
         <v>15</v>
@@ -6342,7 +6342,7 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D120" s="2" t="s">
         <v>257</v>
@@ -6351,16 +6351,16 @@
         <v>258</v>
       </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I120" s="2" t="n">
-        <v>73.53</v>
+        <v>73.46</v>
       </c>
       <c r="J120" s="2" t="s">
         <v>15</v>
@@ -6371,10 +6371,10 @@
         <v>2020</v>
       </c>
       <c r="B121" s="2" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="D121" s="2" t="s">
         <v>259</v>
@@ -6383,16 +6383,16 @@
         <v>260</v>
       </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I121" s="2" t="n">
-        <v>73.48</v>
+        <v>73.42</v>
       </c>
       <c r="J121" s="2" t="s">
         <v>15</v>
@@ -6403,10 +6403,10 @@
         <v>2020</v>
       </c>
       <c r="B122" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D122" s="2" t="s">
         <v>261</v>
@@ -6415,16 +6415,16 @@
         <v>262</v>
       </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I122" s="2" t="n">
-        <v>73.46</v>
+        <v>73.42</v>
       </c>
       <c r="J122" s="2" t="s">
         <v>15</v>
@@ -6435,10 +6435,10 @@
         <v>2020</v>
       </c>
       <c r="B123" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D123" s="2" t="s">
         <v>263</v>
@@ -6447,16 +6447,16 @@
         <v>264</v>
       </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I123" s="2" t="n">
-        <v>73.42</v>
+        <v>73.38</v>
       </c>
       <c r="J123" s="2" t="s">
         <v>15</v>
@@ -6467,10 +6467,10 @@
         <v>2020</v>
       </c>
       <c r="B124" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D124" s="2" t="s">
         <v>265</v>
@@ -6479,16 +6479,16 @@
         <v>266</v>
       </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I124" s="2" t="n">
-        <v>73.42</v>
+        <v>73.29</v>
       </c>
       <c r="J124" s="2" t="s">
         <v>15</v>
@@ -6502,7 +6502,7 @@
         <v>6</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D125" s="2" t="s">
         <v>267</v>
@@ -6511,16 +6511,16 @@
         <v>268</v>
       </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I125" s="2" t="n">
-        <v>73.38</v>
+        <v>73.28</v>
       </c>
       <c r="J125" s="2" t="s">
         <v>15</v>
@@ -6531,10 +6531,10 @@
         <v>2020</v>
       </c>
       <c r="B126" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D126" s="2" t="s">
         <v>269</v>
@@ -6543,16 +6543,16 @@
         <v>270</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I126" s="2" t="n">
-        <v>73.29</v>
+        <v>73.21</v>
       </c>
       <c r="J126" s="2" t="s">
         <v>15</v>
@@ -6563,10 +6563,10 @@
         <v>2020</v>
       </c>
       <c r="B127" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D127" s="2" t="s">
         <v>271</v>
@@ -6575,16 +6575,16 @@
         <v>272</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I127" s="2" t="n">
-        <v>73.28</v>
+        <v>73.21</v>
       </c>
       <c r="J127" s="2" t="s">
         <v>15</v>
@@ -6595,10 +6595,10 @@
         <v>2020</v>
       </c>
       <c r="B128" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D128" s="2" t="s">
         <v>273</v>
@@ -6607,16 +6607,16 @@
         <v>274</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I128" s="2" t="n">
-        <v>73.21</v>
+        <v>73.09</v>
       </c>
       <c r="J128" s="2" t="s">
         <v>15</v>
@@ -6627,10 +6627,10 @@
         <v>2020</v>
       </c>
       <c r="B129" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D129" s="2" t="s">
         <v>275</v>
@@ -6639,16 +6639,16 @@
         <v>276</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I129" s="2" t="n">
-        <v>73.21</v>
+        <v>73.03</v>
       </c>
       <c r="J129" s="2" t="s">
         <v>15</v>
@@ -6659,10 +6659,10 @@
         <v>2020</v>
       </c>
       <c r="B130" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D130" s="2" t="s">
         <v>277</v>
@@ -6671,16 +6671,16 @@
         <v>278</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I130" s="2" t="n">
-        <v>73.09</v>
+        <v>72.98</v>
       </c>
       <c r="J130" s="2" t="s">
         <v>15</v>
@@ -6691,10 +6691,10 @@
         <v>2020</v>
       </c>
       <c r="B131" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D131" s="2" t="s">
         <v>279</v>
@@ -6703,16 +6703,16 @@
         <v>280</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I131" s="2" t="n">
-        <v>73.03</v>
+        <v>72.98</v>
       </c>
       <c r="J131" s="2" t="s">
         <v>15</v>
@@ -6726,7 +6726,7 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D132" s="2" t="s">
         <v>281</v>
@@ -6735,16 +6735,16 @@
         <v>282</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I132" s="2" t="n">
-        <v>72.98</v>
+        <v>72.97</v>
       </c>
       <c r="J132" s="2" t="s">
         <v>15</v>
@@ -6755,10 +6755,10 @@
         <v>2020</v>
       </c>
       <c r="B133" s="2" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>75</v>
+        <v>52</v>
       </c>
       <c r="D133" s="2" t="s">
         <v>283</v>
@@ -6767,16 +6767,16 @@
         <v>284</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I133" s="2" t="n">
-        <v>72.98</v>
+        <v>72.94</v>
       </c>
       <c r="J133" s="2" t="s">
         <v>15</v>
@@ -6790,7 +6790,7 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D134" s="2" t="s">
         <v>285</v>
@@ -6799,16 +6799,16 @@
         <v>286</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I134" s="2" t="n">
-        <v>72.97</v>
+        <v>72.91</v>
       </c>
       <c r="J134" s="2" t="s">
         <v>15</v>
@@ -6819,10 +6819,10 @@
         <v>2020</v>
       </c>
       <c r="B135" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D135" s="2" t="s">
         <v>287</v>
@@ -6831,16 +6831,16 @@
         <v>288</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I135" s="2" t="n">
-        <v>72.94</v>
+        <v>72.89</v>
       </c>
       <c r="J135" s="2" t="s">
         <v>15</v>
@@ -6854,7 +6854,7 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D136" s="2" t="s">
         <v>289</v>
@@ -6863,16 +6863,16 @@
         <v>290</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I136" s="2" t="n">
-        <v>72.91</v>
+        <v>72.86</v>
       </c>
       <c r="J136" s="2" t="s">
         <v>15</v>
@@ -6883,10 +6883,10 @@
         <v>2020</v>
       </c>
       <c r="B137" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>291</v>
@@ -6895,16 +6895,16 @@
         <v>292</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I137" s="2" t="n">
-        <v>72.89</v>
+        <v>72.84</v>
       </c>
       <c r="J137" s="2" t="s">
         <v>15</v>
@@ -6915,10 +6915,10 @@
         <v>2020</v>
       </c>
       <c r="B138" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D138" s="2" t="s">
         <v>293</v>
@@ -6927,16 +6927,16 @@
         <v>294</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I138" s="2" t="n">
-        <v>72.86</v>
+        <v>72.84</v>
       </c>
       <c r="J138" s="2" t="s">
         <v>15</v>
@@ -6947,10 +6947,10 @@
         <v>2020</v>
       </c>
       <c r="B139" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>295</v>
@@ -6959,16 +6959,16 @@
         <v>296</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I139" s="2" t="n">
-        <v>72.84</v>
+        <v>72.66</v>
       </c>
       <c r="J139" s="2" t="s">
         <v>15</v>
@@ -6979,10 +6979,10 @@
         <v>2020</v>
       </c>
       <c r="B140" s="2" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>56</v>
+        <v>71</v>
       </c>
       <c r="D140" s="2" t="s">
         <v>297</v>
@@ -6991,16 +6991,16 @@
         <v>298</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I140" s="2" t="n">
-        <v>72.84</v>
+        <v>72.66</v>
       </c>
       <c r="J140" s="2" t="s">
         <v>15</v>
@@ -7011,10 +7011,10 @@
         <v>2020</v>
       </c>
       <c r="B141" s="2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="D141" s="2" t="s">
         <v>299</v>
@@ -7023,16 +7023,16 @@
         <v>300</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I141" s="2" t="n">
-        <v>72.66</v>
+        <v>72.65</v>
       </c>
       <c r="J141" s="2" t="s">
         <v>15</v>
@@ -7043,10 +7043,10 @@
         <v>2020</v>
       </c>
       <c r="B142" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D142" s="2" t="s">
         <v>301</v>
@@ -7055,16 +7055,16 @@
         <v>302</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I142" s="2" t="n">
-        <v>72.66</v>
+        <v>72.61</v>
       </c>
       <c r="J142" s="2" t="s">
         <v>15</v>
@@ -7078,7 +7078,7 @@
         <v>6</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D143" s="2" t="s">
         <v>303</v>
@@ -7087,16 +7087,16 @@
         <v>304</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I143" s="2" t="n">
-        <v>72.65</v>
+        <v>72.6</v>
       </c>
       <c r="J143" s="2" t="s">
         <v>15</v>
@@ -7107,10 +7107,10 @@
         <v>2020</v>
       </c>
       <c r="B144" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D144" s="2" t="s">
         <v>305</v>
@@ -7119,16 +7119,16 @@
         <v>306</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I144" s="2" t="n">
-        <v>72.61</v>
+        <v>72.56</v>
       </c>
       <c r="J144" s="2" t="s">
         <v>15</v>
@@ -7139,10 +7139,10 @@
         <v>2020</v>
       </c>
       <c r="B145" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D145" s="2" t="s">
         <v>307</v>
@@ -7151,16 +7151,16 @@
         <v>308</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I145" s="2" t="n">
-        <v>72.6</v>
+        <v>72.54</v>
       </c>
       <c r="J145" s="2" t="s">
         <v>15</v>
@@ -7171,10 +7171,10 @@
         <v>2020</v>
       </c>
       <c r="B146" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D146" s="2" t="s">
         <v>309</v>
@@ -7183,16 +7183,16 @@
         <v>310</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I146" s="2" t="n">
-        <v>72.56</v>
+        <v>72.52</v>
       </c>
       <c r="J146" s="2" t="s">
         <v>15</v>
@@ -7203,10 +7203,10 @@
         <v>2020</v>
       </c>
       <c r="B147" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>311</v>
@@ -7215,16 +7215,16 @@
         <v>312</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I147" s="2" t="n">
-        <v>72.54</v>
+        <v>72.52</v>
       </c>
       <c r="J147" s="2" t="s">
         <v>15</v>
@@ -7238,7 +7238,7 @@
         <v>6</v>
       </c>
       <c r="C148" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D148" s="2" t="s">
         <v>313</v>
@@ -7247,16 +7247,16 @@
         <v>314</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I148" s="2" t="n">
-        <v>72.52</v>
+        <v>72.49</v>
       </c>
       <c r="J148" s="2" t="s">
         <v>15</v>
@@ -7270,7 +7270,7 @@
         <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D149" s="2" t="s">
         <v>315</v>
@@ -7279,16 +7279,16 @@
         <v>316</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I149" s="2" t="n">
-        <v>72.52</v>
+        <v>72.47</v>
       </c>
       <c r="J149" s="2" t="s">
         <v>15</v>
@@ -7302,7 +7302,7 @@
         <v>6</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="D150" s="2" t="s">
         <v>317</v>
@@ -7311,16 +7311,16 @@
         <v>318</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I150" s="2" t="n">
-        <v>72.49</v>
+        <v>72.38</v>
       </c>
       <c r="J150" s="2" t="s">
         <v>15</v>
@@ -7334,7 +7334,7 @@
         <v>16</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="D151" s="2" t="s">
         <v>319</v>
@@ -7343,16 +7343,16 @@
         <v>320</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I151" s="2" t="n">
-        <v>72.47</v>
+        <v>72.37</v>
       </c>
       <c r="J151" s="2" t="s">
         <v>15</v>
@@ -7363,10 +7363,10 @@
         <v>2020</v>
       </c>
       <c r="B152" s="2" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D152" s="2" t="s">
         <v>321</v>
@@ -7375,16 +7375,16 @@
         <v>322</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I152" s="2" t="n">
-        <v>72.37</v>
+        <v>72.17</v>
       </c>
       <c r="J152" s="2" t="s">
         <v>15</v>
@@ -7398,7 +7398,7 @@
         <v>13</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D153" s="2" t="s">
         <v>323</v>
@@ -7407,16 +7407,16 @@
         <v>324</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I153" s="2" t="n">
-        <v>72.17</v>
+        <v>72.15</v>
       </c>
       <c r="J153" s="2" t="s">
         <v>15</v>
@@ -7427,10 +7427,10 @@
         <v>2020</v>
       </c>
       <c r="B154" s="2" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>325</v>
@@ -7439,16 +7439,16 @@
         <v>326</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I154" s="2" t="n">
-        <v>72.15</v>
+        <v>72.13</v>
       </c>
       <c r="J154" s="2" t="s">
         <v>15</v>
@@ -7459,10 +7459,10 @@
         <v>2020</v>
       </c>
       <c r="B155" s="2" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>327</v>
@@ -7471,16 +7471,16 @@
         <v>328</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I155" s="2" t="n">
-        <v>72.13</v>
+        <v>72.04</v>
       </c>
       <c r="J155" s="2" t="s">
         <v>15</v>
@@ -7491,10 +7491,10 @@
         <v>2020</v>
       </c>
       <c r="B156" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D156" s="2" t="s">
         <v>329</v>
@@ -7503,16 +7503,16 @@
         <v>330</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I156" s="2" t="n">
-        <v>72.04</v>
+        <v>71.99</v>
       </c>
       <c r="J156" s="2" t="s">
         <v>15</v>
@@ -7526,7 +7526,7 @@
         <v>13</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D157" s="2" t="s">
         <v>331</v>
@@ -7535,16 +7535,16 @@
         <v>332</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I157" s="2" t="n">
-        <v>71.99</v>
+        <v>71.96</v>
       </c>
       <c r="J157" s="2" t="s">
         <v>15</v>
@@ -7555,10 +7555,10 @@
         <v>2020</v>
       </c>
       <c r="B158" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D158" s="2" t="s">
         <v>333</v>
@@ -7567,16 +7567,16 @@
         <v>334</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I158" s="2" t="n">
-        <v>71.96</v>
+        <v>71.81</v>
       </c>
       <c r="J158" s="2" t="s">
         <v>15</v>
@@ -7587,10 +7587,10 @@
         <v>2020</v>
       </c>
       <c r="B159" s="2" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>70</v>
+        <v>45</v>
       </c>
       <c r="D159" s="2" t="s">
         <v>335</v>
@@ -7599,16 +7599,16 @@
         <v>336</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I159" s="2" t="n">
-        <v>71.81</v>
+        <v>71.79</v>
       </c>
       <c r="J159" s="2" t="s">
         <v>15</v>
@@ -7622,7 +7622,7 @@
         <v>13</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>337</v>
@@ -7631,16 +7631,16 @@
         <v>338</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I160" s="2" t="n">
-        <v>71.79</v>
+        <v>71.69</v>
       </c>
       <c r="J160" s="2" t="s">
         <v>15</v>
@@ -7654,7 +7654,7 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>339</v>
@@ -7663,16 +7663,16 @@
         <v>340</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I161" s="2" t="n">
-        <v>71.69</v>
+        <v>71.65</v>
       </c>
       <c r="J161" s="2" t="s">
         <v>15</v>
@@ -7683,10 +7683,10 @@
         <v>2020</v>
       </c>
       <c r="B162" s="2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>49</v>
+        <v>66</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>341</v>
@@ -7695,16 +7695,16 @@
         <v>342</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I162" s="2" t="n">
-        <v>71.65</v>
+        <v>71.63</v>
       </c>
       <c r="J162" s="2" t="s">
         <v>15</v>
@@ -7715,10 +7715,10 @@
         <v>2020</v>
       </c>
       <c r="B163" s="2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>343</v>
@@ -7727,16 +7727,16 @@
         <v>344</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I163" s="2" t="n">
-        <v>71.63</v>
+        <v>71.47</v>
       </c>
       <c r="J163" s="2" t="s">
         <v>15</v>
@@ -7747,10 +7747,10 @@
         <v>2020</v>
       </c>
       <c r="B164" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D164" s="2" t="s">
         <v>345</v>
@@ -7759,16 +7759,16 @@
         <v>346</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I164" s="2" t="n">
-        <v>71.47</v>
+        <v>71.23</v>
       </c>
       <c r="J164" s="2" t="s">
         <v>15</v>
@@ -7779,10 +7779,10 @@
         <v>2020</v>
       </c>
       <c r="B165" s="2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="D165" s="2" t="s">
         <v>347</v>
@@ -7791,16 +7791,16 @@
         <v>348</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I165" s="2" t="n">
-        <v>71.23</v>
+        <v>71.21</v>
       </c>
       <c r="J165" s="2" t="s">
         <v>15</v>
@@ -7811,10 +7811,10 @@
         <v>2020</v>
       </c>
       <c r="B166" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D166" s="2" t="s">
         <v>349</v>
@@ -7823,16 +7823,16 @@
         <v>350</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I166" s="2" t="n">
-        <v>71.21</v>
+        <v>70.87</v>
       </c>
       <c r="J166" s="2" t="s">
         <v>15</v>
@@ -7843,10 +7843,10 @@
         <v>2020</v>
       </c>
       <c r="B167" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D167" s="2" t="s">
         <v>351</v>
@@ -7855,16 +7855,16 @@
         <v>352</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I167" s="2" t="n">
-        <v>70.87</v>
+        <v>70.72</v>
       </c>
       <c r="J167" s="2" t="s">
         <v>15</v>
@@ -7875,10 +7875,10 @@
         <v>2020</v>
       </c>
       <c r="B168" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D168" s="2" t="s">
         <v>353</v>
@@ -7887,16 +7887,16 @@
         <v>354</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I168" s="2" t="n">
-        <v>70.72</v>
+        <v>70.7</v>
       </c>
       <c r="J168" s="2" t="s">
         <v>15</v>
@@ -7907,10 +7907,10 @@
         <v>2020</v>
       </c>
       <c r="B169" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>355</v>
@@ -7919,16 +7919,16 @@
         <v>356</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I169" s="2" t="n">
-        <v>70.7</v>
+        <v>70.62</v>
       </c>
       <c r="J169" s="2" t="s">
         <v>15</v>
@@ -7939,10 +7939,10 @@
         <v>2020</v>
       </c>
       <c r="B170" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D170" s="2" t="s">
         <v>357</v>
@@ -7951,16 +7951,16 @@
         <v>358</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I170" s="2" t="n">
-        <v>70.62</v>
+        <v>70.6</v>
       </c>
       <c r="J170" s="2" t="s">
         <v>15</v>
@@ -7971,10 +7971,10 @@
         <v>2020</v>
       </c>
       <c r="B171" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>359</v>
@@ -7983,10 +7983,10 @@
         <v>360</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8003,10 +8003,10 @@
         <v>2020</v>
       </c>
       <c r="B172" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>361</v>
@@ -8015,16 +8015,16 @@
         <v>362</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I172" s="2" t="n">
-        <v>70.6</v>
+        <v>70.51</v>
       </c>
       <c r="J172" s="2" t="s">
         <v>15</v>
@@ -8038,7 +8038,7 @@
         <v>13</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>363</v>
@@ -8047,16 +8047,16 @@
         <v>364</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I173" s="2" t="n">
-        <v>70.51</v>
+        <v>70.41</v>
       </c>
       <c r="J173" s="2" t="s">
         <v>15</v>
@@ -8067,10 +8067,10 @@
         <v>2020</v>
       </c>
       <c r="B174" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D174" s="2" t="s">
         <v>365</v>
@@ -8079,16 +8079,16 @@
         <v>366</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I174" s="2" t="n">
-        <v>70.41</v>
+        <v>69.93</v>
       </c>
       <c r="J174" s="2" t="s">
         <v>15</v>
@@ -8099,10 +8099,10 @@
         <v>2020</v>
       </c>
       <c r="B175" s="2" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="D175" s="2" t="s">
         <v>367</v>
@@ -8111,16 +8111,16 @@
         <v>368</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I175" s="2" t="n">
-        <v>69.93</v>
+        <v>69.8</v>
       </c>
       <c r="J175" s="2" t="s">
         <v>15</v>
@@ -8134,7 +8134,7 @@
         <v>13</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D176" s="2" t="s">
         <v>369</v>
@@ -8143,16 +8143,16 @@
         <v>370</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I176" s="2" t="n">
-        <v>69.8</v>
+        <v>69.21</v>
       </c>
       <c r="J176" s="2" t="s">
         <v>15</v>
@@ -8163,10 +8163,10 @@
         <v>2020</v>
       </c>
       <c r="B177" s="2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="D177" s="2" t="s">
         <v>371</v>
@@ -8175,10 +8175,10 @@
         <v>372</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8195,10 +8195,10 @@
         <v>2020</v>
       </c>
       <c r="B178" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D178" s="2" t="s">
         <v>373</v>
@@ -8207,16 +8207,16 @@
         <v>374</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I178" s="2" t="n">
-        <v>69.21</v>
+        <v>68.72</v>
       </c>
       <c r="J178" s="2" t="s">
         <v>15</v>
@@ -8227,10 +8227,10 @@
         <v>2020</v>
       </c>
       <c r="B179" s="2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="D179" s="2" t="s">
         <v>375</v>
@@ -8239,16 +8239,16 @@
         <v>376</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I179" s="2" t="n">
-        <v>68.72</v>
+        <v>67.94</v>
       </c>
       <c r="J179" s="2" t="s">
         <v>15</v>
@@ -8259,10 +8259,10 @@
         <v>2020</v>
       </c>
       <c r="B180" s="2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>59</v>
+        <v>52</v>
       </c>
       <c r="D180" s="2" t="s">
         <v>377</v>
@@ -8271,16 +8271,16 @@
         <v>378</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I180" s="2" t="n">
-        <v>67.94</v>
+        <v>67.58</v>
       </c>
       <c r="J180" s="2" t="s">
         <v>15</v>
@@ -8291,10 +8291,10 @@
         <v>2020</v>
       </c>
       <c r="B181" s="2" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="D181" s="2" t="s">
         <v>379</v>
@@ -8303,16 +8303,16 @@
         <v>380</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I181" s="2" t="n">
-        <v>67.58</v>
+        <v>67.44</v>
       </c>
       <c r="J181" s="2" t="s">
         <v>15</v>
@@ -8326,7 +8326,7 @@
         <v>13</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>381</v>
@@ -8335,16 +8335,16 @@
         <v>382</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I182" s="2" t="n">
-        <v>67.44</v>
+        <v>67.04</v>
       </c>
       <c r="J182" s="2" t="s">
         <v>15</v>
@@ -8358,7 +8358,7 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>383</v>
@@ -8367,16 +8367,16 @@
         <v>384</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I183" s="2" t="n">
-        <v>67.04</v>
+        <v>59.64</v>
       </c>
       <c r="J183" s="2" t="s">
         <v>15</v>
@@ -8390,7 +8390,7 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>385</v>
@@ -8399,16 +8399,16 @@
         <v>386</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I184" s="2" t="n">
-        <v>59.64</v>
+        <v>58.23</v>
       </c>
       <c r="J184" s="2" t="s">
         <v>15</v>
@@ -8419,28 +8419,28 @@
         <v>2020</v>
       </c>
       <c r="B185" s="2" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>49</v>
+        <v>387</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>390</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>391</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I185" s="2" t="n">
-        <v>58.23</v>
+        <v>82.55</v>
       </c>
       <c r="J185" s="2" t="s">
         <v>15</v>
@@ -8451,28 +8451,28 @@
         <v>2020</v>
       </c>
       <c r="B186" s="2" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D186" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="E186" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="F186" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="E186" s="2" t="s">
+      <c r="G186" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="F186" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="G186" s="2" t="s">
-        <v>393</v>
-      </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I186" s="2" t="n">
-        <v>82.55</v>
+        <v>79.12</v>
       </c>
       <c r="J186" s="2" t="s">
         <v>15</v>
@@ -8483,28 +8483,28 @@
         <v>2020</v>
       </c>
       <c r="B187" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D187" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E187" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G187" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I187" s="2" t="n">
-        <v>79.12</v>
+        <v>77.71</v>
       </c>
       <c r="J187" s="2" t="s">
         <v>15</v>
@@ -8518,7 +8518,7 @@
         <v>4</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D188" s="2" t="s">
         <v>398</v>
@@ -8527,16 +8527,16 @@
         <v>399</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I188" s="2" t="n">
-        <v>77.71</v>
+        <v>77.08</v>
       </c>
       <c r="J188" s="2" t="s">
         <v>15</v>
@@ -8547,10 +8547,10 @@
         <v>2020</v>
       </c>
       <c r="B189" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D189" s="2" t="s">
         <v>400</v>
@@ -8559,16 +8559,16 @@
         <v>401</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I189" s="2" t="n">
-        <v>77.08</v>
+        <v>76.56</v>
       </c>
       <c r="J189" s="2" t="s">
         <v>15</v>
@@ -8579,10 +8579,10 @@
         <v>2020</v>
       </c>
       <c r="B190" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D190" s="2" t="s">
         <v>402</v>
@@ -8591,16 +8591,16 @@
         <v>403</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I190" s="2" t="n">
-        <v>76.56</v>
+        <v>76.52</v>
       </c>
       <c r="J190" s="2" t="s">
         <v>15</v>
@@ -8614,25 +8614,25 @@
         <v>4</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>404</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>405</v>
+        <v>395</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I191" s="2" t="n">
-        <v>76.52</v>
+        <v>76.44</v>
       </c>
       <c r="J191" s="2" t="s">
         <v>15</v>
@@ -8643,28 +8643,28 @@
         <v>2020</v>
       </c>
       <c r="B192" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D192" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="E192" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="E192" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="F192" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I192" s="2" t="n">
-        <v>76.44</v>
+        <v>76.3</v>
       </c>
       <c r="J192" s="2" t="s">
         <v>15</v>
@@ -8675,10 +8675,10 @@
         <v>2020</v>
       </c>
       <c r="B193" s="2" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>394</v>
+        <v>387</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>407</v>
@@ -8687,16 +8687,16 @@
         <v>408</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I193" s="2" t="n">
-        <v>76.3</v>
+        <v>76.19</v>
       </c>
       <c r="J193" s="2" t="s">
         <v>15</v>
@@ -8707,10 +8707,10 @@
         <v>2020</v>
       </c>
       <c r="B194" s="2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>409</v>
@@ -8719,16 +8719,16 @@
         <v>410</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I194" s="2" t="n">
-        <v>76.19</v>
+        <v>76.03</v>
       </c>
       <c r="J194" s="2" t="s">
         <v>15</v>
@@ -8739,10 +8739,10 @@
         <v>2020</v>
       </c>
       <c r="B195" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>411</v>
@@ -8751,16 +8751,16 @@
         <v>412</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I195" s="2" t="n">
-        <v>76.03</v>
+        <v>76.01</v>
       </c>
       <c r="J195" s="2" t="s">
         <v>15</v>
@@ -8774,7 +8774,7 @@
         <v>3</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>413</v>
@@ -8783,16 +8783,16 @@
         <v>414</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I196" s="2" t="n">
-        <v>76.01</v>
+        <v>75.51</v>
       </c>
       <c r="J196" s="2" t="s">
         <v>15</v>
@@ -8806,7 +8806,7 @@
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D197" s="2" t="s">
         <v>415</v>
@@ -8815,16 +8815,16 @@
         <v>416</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I197" s="2" t="n">
-        <v>75.51</v>
+        <v>75.45</v>
       </c>
       <c r="J197" s="2" t="s">
         <v>15</v>
@@ -8835,28 +8835,28 @@
         <v>2020</v>
       </c>
       <c r="B198" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I198" s="2" t="n">
-        <v>75.45</v>
+        <v>75.23</v>
       </c>
       <c r="J198" s="2" t="s">
         <v>15</v>
@@ -8867,10 +8867,10 @@
         <v>2020</v>
       </c>
       <c r="B199" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>419</v>
+        <v>392</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>420</v>
@@ -8879,16 +8879,16 @@
         <v>421</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I199" s="2" t="n">
-        <v>75.23</v>
+        <v>74.46</v>
       </c>
       <c r="J199" s="2" t="s">
         <v>15</v>
@@ -8899,10 +8899,10 @@
         <v>2020</v>
       </c>
       <c r="B200" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>422</v>
@@ -8911,16 +8911,16 @@
         <v>423</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I200" s="2" t="n">
-        <v>74.46</v>
+        <v>74.37</v>
       </c>
       <c r="J200" s="2" t="s">
         <v>15</v>
@@ -8931,10 +8931,10 @@
         <v>2020</v>
       </c>
       <c r="B201" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>397</v>
+        <v>392</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>424</v>
@@ -8943,16 +8943,16 @@
         <v>425</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I201" s="2" t="n">
-        <v>74.37</v>
+        <v>74.32</v>
       </c>
       <c r="J201" s="2" t="s">
         <v>15</v>
@@ -8963,10 +8963,10 @@
         <v>2020</v>
       </c>
       <c r="B202" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>394</v>
+        <v>417</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>426</v>
@@ -8975,16 +8975,16 @@
         <v>427</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I202" s="2" t="n">
-        <v>74.32</v>
+        <v>74.29</v>
       </c>
       <c r="J202" s="2" t="s">
         <v>15</v>
@@ -8995,10 +8995,10 @@
         <v>2020</v>
       </c>
       <c r="B203" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>419</v>
+        <v>395</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>428</v>
@@ -9007,16 +9007,16 @@
         <v>429</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I203" s="2" t="n">
-        <v>74.29</v>
+        <v>74.27</v>
       </c>
       <c r="J203" s="2" t="s">
         <v>15</v>
@@ -9030,7 +9030,7 @@
         <v>4</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>430</v>
@@ -9039,16 +9039,16 @@
         <v>431</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I204" s="2" t="n">
-        <v>74.27</v>
+        <v>74.24</v>
       </c>
       <c r="J204" s="2" t="s">
         <v>15</v>
@@ -9059,28 +9059,28 @@
         <v>2020</v>
       </c>
       <c r="B205" s="2" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>397</v>
+        <v>432</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I205" s="2" t="n">
-        <v>74.24</v>
+        <v>74.21</v>
       </c>
       <c r="J205" s="2" t="s">
         <v>15</v>
@@ -9091,10 +9091,10 @@
         <v>2020</v>
       </c>
       <c r="B206" s="2" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>434</v>
+        <v>395</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>435</v>
@@ -9103,16 +9103,16 @@
         <v>436</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I206" s="2" t="n">
-        <v>74.21</v>
+        <v>74.1</v>
       </c>
       <c r="J206" s="2" t="s">
         <v>15</v>
@@ -9126,7 +9126,7 @@
         <v>4</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>437</v>
@@ -9135,16 +9135,16 @@
         <v>438</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I207" s="2" t="n">
-        <v>74.1</v>
+        <v>74.06</v>
       </c>
       <c r="J207" s="2" t="s">
         <v>15</v>
@@ -9158,7 +9158,7 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>439</v>
@@ -9167,10 +9167,10 @@
         <v>440</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9190,7 +9190,7 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>441</v>
@@ -9199,10 +9199,10 @@
         <v>442</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9222,19 +9222,19 @@
         <v>2</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>443</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9254,7 +9254,7 @@
         <v>1</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>444</v>
@@ -9263,10 +9263,10 @@
         <v>445</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9286,7 +9286,7 @@
         <v>4</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>446</v>
@@ -9295,10 +9295,10 @@
         <v>447</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9318,7 +9318,7 @@
         <v>2</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>448</v>
@@ -9327,10 +9327,10 @@
         <v>449</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9350,7 +9350,7 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>450</v>
@@ -9359,10 +9359,10 @@
         <v>451</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9382,7 +9382,7 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>452</v>
@@ -9391,10 +9391,10 @@
         <v>453</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9414,7 +9414,7 @@
         <v>1</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>454</v>
@@ -9423,10 +9423,10 @@
         <v>455</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9446,7 +9446,7 @@
         <v>4</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>456</v>
@@ -9455,10 +9455,10 @@
         <v>457</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9478,7 +9478,7 @@
         <v>3</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>458</v>
@@ -9487,10 +9487,10 @@
         <v>459</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9510,7 +9510,7 @@
         <v>2</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D219" s="2" t="s">
         <v>460</v>
@@ -9519,10 +9519,10 @@
         <v>461</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9542,7 +9542,7 @@
         <v>1</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D220" s="2" t="s">
         <v>462</v>
@@ -9551,10 +9551,10 @@
         <v>463</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9574,7 +9574,7 @@
         <v>1</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>464</v>
@@ -9583,10 +9583,10 @@
         <v>465</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9606,7 +9606,7 @@
         <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>466</v>
@@ -9615,10 +9615,10 @@
         <v>467</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9638,7 +9638,7 @@
         <v>2</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>468</v>
@@ -9647,10 +9647,10 @@
         <v>469</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9670,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>470</v>
@@ -9679,10 +9679,10 @@
         <v>471</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9702,7 +9702,7 @@
         <v>2</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="D225" s="2" t="s">
         <v>472</v>
@@ -9711,10 +9711,10 @@
         <v>473</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>392</v>
+        <v>390</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -448,18 +448,18 @@
     <t xml:space="preserve">San Fernando</t>
   </si>
   <si>
+    <t xml:space="preserve">5404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petorca</t>
+  </si>
+  <si>
     <t xml:space="preserve">5502</t>
   </si>
   <si>
     <t xml:space="preserve">Calera</t>
   </si>
   <si>
-    <t xml:space="preserve">5404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petorca</t>
-  </si>
-  <si>
     <t xml:space="preserve">7306</t>
   </si>
   <si>
@@ -892,18 +892,18 @@
     <t xml:space="preserve">San Pedro</t>
   </si>
   <si>
+    <t xml:space="preserve">6113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pichidegua</t>
+  </si>
+  <si>
     <t xml:space="preserve">6304</t>
   </si>
   <si>
     <t xml:space="preserve">Lolol</t>
   </si>
   <si>
-    <t xml:space="preserve">6113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pichidegua</t>
-  </si>
-  <si>
     <t xml:space="preserve">7108</t>
   </si>
   <si>
@@ -1507,18 +1507,18 @@
     <t xml:space="preserve">Los Rios</t>
   </si>
   <si>
+    <t xml:space="preserve">14101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valdivia</t>
+  </si>
+  <si>
     <t xml:space="preserve">14201</t>
   </si>
   <si>
     <t xml:space="preserve">La Unión</t>
   </si>
   <si>
-    <t xml:space="preserve">14101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Valdivia</t>
-  </si>
-  <si>
     <t xml:space="preserve">10109</t>
   </si>
   <si>
@@ -2104,7 +2104,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 20:00</t>
+    <t xml:space="preserve">2026-09-18 11:24</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
+++ b/output/graficos_nacionales/plot_nacional_e_mat_a_2020.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="714" uniqueCount="714">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="712" uniqueCount="712">
   <si>
     <t xml:space="preserve">year</t>
   </si>
@@ -49,7 +49,7 @@
     <t xml:space="preserve">metric_label</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysen</t>
+    <t xml:space="preserve">Aysén</t>
   </si>
   <si>
     <t xml:space="preserve">11202</t>
@@ -94,9 +94,6 @@
     <t xml:space="preserve">11201</t>
   </si>
   <si>
-    <t xml:space="preserve">Aysén</t>
-  </si>
-  <si>
     <t xml:space="preserve">Magallanes</t>
   </si>
   <si>
@@ -193,7 +190,7 @@
     <t xml:space="preserve">Machalí</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaiso</t>
+    <t xml:space="preserve">Valparaíso</t>
   </si>
   <si>
     <t xml:space="preserve">5504</t>
@@ -241,7 +238,7 @@
     <t xml:space="preserve">Colina</t>
   </si>
   <si>
-    <t xml:space="preserve">Nuble</t>
+    <t xml:space="preserve">Ñuble</t>
   </si>
   <si>
     <t xml:space="preserve">16101</t>
@@ -616,7 +613,7 @@
     <t xml:space="preserve">16206</t>
   </si>
   <si>
-    <t xml:space="preserve">Ranquil</t>
+    <t xml:space="preserve">Ránquil</t>
   </si>
   <si>
     <t xml:space="preserve">5601</t>
@@ -826,9 +823,6 @@
     <t xml:space="preserve">5101</t>
   </si>
   <si>
-    <t xml:space="preserve">Valparaíso</t>
-  </si>
-  <si>
     <t xml:space="preserve">6309</t>
   </si>
   <si>
@@ -1324,7 +1318,7 @@
     <t xml:space="preserve">Río Hurtado</t>
   </si>
   <si>
-    <t xml:space="preserve">Tarapaca</t>
+    <t xml:space="preserve">Tarapacá</t>
   </si>
   <si>
     <t xml:space="preserve">1107</t>
@@ -1450,7 +1444,7 @@
     <t xml:space="preserve">San Pedro de Atacama</t>
   </si>
   <si>
-    <t xml:space="preserve">Biobio</t>
+    <t xml:space="preserve">Biobío</t>
   </si>
   <si>
     <t xml:space="preserve">8108</t>
@@ -1498,7 +1492,7 @@
     <t xml:space="preserve">Talcahuano</t>
   </si>
   <si>
-    <t xml:space="preserve">La Araucania</t>
+    <t xml:space="preserve">La Araucanía</t>
   </si>
   <si>
     <t xml:space="preserve">9101</t>
@@ -1513,7 +1507,7 @@
     <t xml:space="preserve">Penco</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Rios</t>
+    <t xml:space="preserve">Los Ríos</t>
   </si>
   <si>
     <t xml:space="preserve">14201</t>
@@ -1639,7 +1633,7 @@
     <t xml:space="preserve">8206</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Alamos</t>
+    <t xml:space="preserve">Los Álamos</t>
   </si>
   <si>
     <t xml:space="preserve">14107</t>
@@ -1741,7 +1735,7 @@
     <t xml:space="preserve">8301</t>
   </si>
   <si>
-    <t xml:space="preserve">Los Angeles</t>
+    <t xml:space="preserve">Los Ángeles</t>
   </si>
   <si>
     <t xml:space="preserve">10404</t>
@@ -2113,7 +2107,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:16</t>
+    <t xml:space="preserve">2026-10-05 17:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -2741,7 +2735,7 @@
         <v>24</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>13</v>
@@ -2767,13 +2761,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="E8" s="2" t="s">
         <v>27</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>28</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>13</v>
@@ -2799,13 +2793,13 @@
         <v>12</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D9" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>29</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>30</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>13</v>
@@ -2834,10 +2828,10 @@
         <v>10</v>
       </c>
       <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>31</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>32</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>13</v>
@@ -2866,10 +2860,10 @@
         <v>10</v>
       </c>
       <c r="D11" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>13</v>
@@ -2895,13 +2889,13 @@
         <v>12</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>36</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>13</v>
@@ -2930,10 +2924,10 @@
         <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>38</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>13</v>
@@ -2962,10 +2956,10 @@
         <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>40</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>13</v>
@@ -2991,13 +2985,13 @@
         <v>12</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D15" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>13</v>
@@ -3023,13 +3017,13 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D16" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>13</v>
@@ -3055,13 +3049,13 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D17" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>46</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>13</v>
@@ -3087,13 +3081,13 @@
         <v>12</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D18" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>47</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>48</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>13</v>
@@ -3119,19 +3113,19 @@
         <v>13</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="E19" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E19" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>15</v>
@@ -3151,19 +3145,19 @@
         <v>13</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="E20" s="2" t="s">
-        <v>55</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>15</v>
@@ -3186,16 +3180,16 @@
         <v>17</v>
       </c>
       <c r="D21" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E21" s="2" t="s">
-        <v>57</v>
-      </c>
       <c r="F21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>15</v>
@@ -3215,19 +3209,19 @@
         <v>5</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="D22" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="E22" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E22" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>15</v>
@@ -3247,19 +3241,19 @@
         <v>13</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D23" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="E23" s="2" t="s">
-        <v>62</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>15</v>
@@ -3279,19 +3273,19 @@
         <v>5</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="E24" s="2" t="s">
-        <v>64</v>
-      </c>
       <c r="F24" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>15</v>
@@ -3311,19 +3305,19 @@
         <v>13</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D25" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="2" t="s">
-        <v>66</v>
-      </c>
       <c r="F25" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>15</v>
@@ -3343,19 +3337,19 @@
         <v>5</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D26" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="E26" s="2" t="s">
-        <v>68</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>15</v>
@@ -3375,19 +3369,19 @@
         <v>7</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D27" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="E27" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E27" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="F27" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>15</v>
@@ -3407,19 +3401,19 @@
         <v>13</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D28" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="E28" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="F28" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>15</v>
@@ -3439,19 +3433,19 @@
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="D29" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="E29" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="E29" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>15</v>
@@ -3471,19 +3465,19 @@
         <v>5</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="E30" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F30" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>15</v>
@@ -3503,19 +3497,19 @@
         <v>5</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D31" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="E31" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="F31" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>15</v>
@@ -3535,19 +3529,19 @@
         <v>7</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D32" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="E32" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="E32" s="2" t="s">
-        <v>82</v>
-      </c>
       <c r="F32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>15</v>
@@ -3567,19 +3561,19 @@
         <v>7</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D33" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E33" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="E33" s="2" t="s">
-        <v>84</v>
-      </c>
       <c r="F33" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G33" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H33" s="2" t="s">
         <v>15</v>
@@ -3599,19 +3593,19 @@
         <v>7</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D34" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="E34" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E34" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="F34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H34" s="2" t="s">
         <v>15</v>
@@ -3631,19 +3625,19 @@
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D35" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E35" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="E35" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="F35" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G35" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H35" s="2" t="s">
         <v>15</v>
@@ -3663,19 +3657,19 @@
         <v>5</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E36" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>90</v>
-      </c>
       <c r="F36" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H36" s="2" t="s">
         <v>15</v>
@@ -3695,19 +3689,19 @@
         <v>16</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D37" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E37" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E37" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="F37" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G37" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H37" s="2" t="s">
         <v>15</v>
@@ -3727,19 +3721,19 @@
         <v>5</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D38" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E38" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="E38" s="2" t="s">
-        <v>94</v>
-      </c>
       <c r="F38" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G38" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H38" s="2" t="s">
         <v>15</v>
@@ -3759,19 +3753,19 @@
         <v>5</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D39" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E39" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>96</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G39" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H39" s="2" t="s">
         <v>15</v>
@@ -3794,16 +3788,16 @@
         <v>17</v>
       </c>
       <c r="D40" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E40" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E40" s="2" t="s">
-        <v>98</v>
-      </c>
       <c r="F40" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G40" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H40" s="2" t="s">
         <v>15</v>
@@ -3823,19 +3817,19 @@
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D41" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="E41" s="2" t="s">
-        <v>100</v>
-      </c>
       <c r="F41" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H41" s="2" t="s">
         <v>15</v>
@@ -3855,19 +3849,19 @@
         <v>13</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D42" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="E42" s="2" t="s">
-        <v>102</v>
-      </c>
       <c r="F42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H42" s="2" t="s">
         <v>15</v>
@@ -3887,19 +3881,19 @@
         <v>5</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D43" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E43" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="E43" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="F43" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>15</v>
@@ -3919,19 +3913,19 @@
         <v>13</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D44" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E44" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="E44" s="2" t="s">
-        <v>106</v>
-      </c>
       <c r="F44" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H44" s="2" t="s">
         <v>15</v>
@@ -3954,16 +3948,16 @@
         <v>17</v>
       </c>
       <c r="D45" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E45" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E45" s="2" t="s">
-        <v>108</v>
-      </c>
       <c r="F45" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H45" s="2" t="s">
         <v>15</v>
@@ -3983,19 +3977,19 @@
         <v>7</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D46" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E46" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="E46" s="2" t="s">
-        <v>110</v>
-      </c>
       <c r="F46" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H46" s="2" t="s">
         <v>15</v>
@@ -4018,16 +4012,16 @@
         <v>17</v>
       </c>
       <c r="D47" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="2" t="s">
-        <v>112</v>
-      </c>
       <c r="F47" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H47" s="2" t="s">
         <v>15</v>
@@ -4047,19 +4041,19 @@
         <v>7</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H48" s="2" t="s">
         <v>15</v>
@@ -4079,19 +4073,19 @@
         <v>7</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D49" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E49" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="E49" s="2" t="s">
-        <v>115</v>
-      </c>
       <c r="F49" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H49" s="2" t="s">
         <v>15</v>
@@ -4111,19 +4105,19 @@
         <v>5</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="E50" s="2" t="s">
-        <v>117</v>
-      </c>
       <c r="F50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>15</v>
@@ -4143,19 +4137,19 @@
         <v>5</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E51" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="E51" s="2" t="s">
-        <v>119</v>
-      </c>
       <c r="F51" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H51" s="2" t="s">
         <v>15</v>
@@ -4175,19 +4169,19 @@
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D52" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E52" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="E52" s="2" t="s">
-        <v>121</v>
-      </c>
       <c r="F52" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H52" s="2" t="s">
         <v>15</v>
@@ -4207,19 +4201,19 @@
         <v>5</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D53" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="E53" s="2" t="s">
-        <v>123</v>
-      </c>
       <c r="F53" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H53" s="2" t="s">
         <v>15</v>
@@ -4239,19 +4233,19 @@
         <v>7</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D54" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E54" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="E54" s="2" t="s">
-        <v>125</v>
-      </c>
       <c r="F54" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G54" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H54" s="2" t="s">
         <v>15</v>
@@ -4271,19 +4265,19 @@
         <v>7</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D55" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E55" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="E55" s="2" t="s">
-        <v>127</v>
-      </c>
       <c r="F55" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>15</v>
@@ -4303,19 +4297,19 @@
         <v>13</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D56" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E56" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E56" s="2" t="s">
-        <v>129</v>
-      </c>
       <c r="F56" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G56" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H56" s="2" t="s">
         <v>15</v>
@@ -4338,16 +4332,16 @@
         <v>17</v>
       </c>
       <c r="D57" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E57" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="E57" s="2" t="s">
-        <v>131</v>
-      </c>
       <c r="F57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H57" s="2" t="s">
         <v>15</v>
@@ -4370,16 +4364,16 @@
         <v>17</v>
       </c>
       <c r="D58" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E58" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="E58" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="F58" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G58" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H58" s="2" t="s">
         <v>15</v>
@@ -4399,19 +4393,19 @@
         <v>13</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D59" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E59" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="E59" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="F59" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G59" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H59" s="2" t="s">
         <v>15</v>
@@ -4431,19 +4425,19 @@
         <v>5</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D60" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E60" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="E60" s="2" t="s">
-        <v>137</v>
-      </c>
       <c r="F60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>15</v>
@@ -4463,19 +4457,19 @@
         <v>5</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D61" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E61" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="E61" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="F61" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>15</v>
@@ -4495,19 +4489,19 @@
         <v>13</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D62" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E62" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="E62" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="F62" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>15</v>
@@ -4527,19 +4521,19 @@
         <v>5</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="E63" s="2" t="s">
-        <v>143</v>
-      </c>
       <c r="F63" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G63" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H63" s="2" t="s">
         <v>15</v>
@@ -4562,16 +4556,16 @@
         <v>17</v>
       </c>
       <c r="D64" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E64" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="E64" s="2" t="s">
-        <v>145</v>
-      </c>
       <c r="F64" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G64" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H64" s="2" t="s">
         <v>15</v>
@@ -4591,19 +4585,19 @@
         <v>5</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D65" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="E65" s="2" t="s">
-        <v>147</v>
-      </c>
       <c r="F65" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G65" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H65" s="2" t="s">
         <v>15</v>
@@ -4623,19 +4617,19 @@
         <v>5</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D66" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="E66" s="2" t="s">
-        <v>149</v>
-      </c>
       <c r="F66" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G66" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H66" s="2" t="s">
         <v>15</v>
@@ -4655,19 +4649,19 @@
         <v>7</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D67" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="E67" s="2" t="s">
-        <v>151</v>
-      </c>
       <c r="F67" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G67" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H67" s="2" t="s">
         <v>15</v>
@@ -4687,19 +4681,19 @@
         <v>7</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D68" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E68" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="E68" s="2" t="s">
-        <v>153</v>
-      </c>
       <c r="F68" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>15</v>
@@ -4722,16 +4716,16 @@
         <v>17</v>
       </c>
       <c r="D69" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E69" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="E69" s="2" t="s">
-        <v>155</v>
-      </c>
       <c r="F69" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H69" s="2" t="s">
         <v>15</v>
@@ -4751,19 +4745,19 @@
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D70" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="E70" s="2" t="s">
-        <v>157</v>
-      </c>
       <c r="F70" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G70" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H70" s="2" t="s">
         <v>15</v>
@@ -4783,19 +4777,19 @@
         <v>7</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D71" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E71" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="E71" s="2" t="s">
-        <v>159</v>
-      </c>
       <c r="F71" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>15</v>
@@ -4815,19 +4809,19 @@
         <v>5</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D72" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E72" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="E72" s="2" t="s">
-        <v>161</v>
-      </c>
       <c r="F72" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G72" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H72" s="2" t="s">
         <v>15</v>
@@ -4847,19 +4841,19 @@
         <v>7</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D73" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E73" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="E73" s="2" t="s">
-        <v>163</v>
-      </c>
       <c r="F73" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H73" s="2" t="s">
         <v>15</v>
@@ -4882,16 +4876,16 @@
         <v>17</v>
       </c>
       <c r="D74" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E74" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="E74" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="F74" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G74" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H74" s="2" t="s">
         <v>15</v>
@@ -4911,19 +4905,19 @@
         <v>7</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D75" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E75" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="E75" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="F75" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G75" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H75" s="2" t="s">
         <v>15</v>
@@ -4943,19 +4937,19 @@
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D76" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E76" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="E76" s="2" t="s">
-        <v>169</v>
-      </c>
       <c r="F76" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H76" s="2" t="s">
         <v>15</v>
@@ -4978,16 +4972,16 @@
         <v>17</v>
       </c>
       <c r="D77" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E77" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="E77" s="2" t="s">
-        <v>171</v>
-      </c>
       <c r="F77" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>15</v>
@@ -5007,19 +5001,19 @@
         <v>5</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D78" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E78" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="E78" s="2" t="s">
-        <v>173</v>
-      </c>
       <c r="F78" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G78" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H78" s="2" t="s">
         <v>15</v>
@@ -5039,19 +5033,19 @@
         <v>7</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D79" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E79" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="E79" s="2" t="s">
-        <v>175</v>
-      </c>
       <c r="F79" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G79" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H79" s="2" t="s">
         <v>15</v>
@@ -5074,16 +5068,16 @@
         <v>17</v>
       </c>
       <c r="D80" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="E80" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="F80" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G80" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H80" s="2" t="s">
         <v>15</v>
@@ -5106,16 +5100,16 @@
         <v>17</v>
       </c>
       <c r="D81" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="E81" s="2" t="s">
-        <v>179</v>
-      </c>
       <c r="F81" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G81" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H81" s="2" t="s">
         <v>15</v>
@@ -5135,19 +5129,19 @@
         <v>7</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D82" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="E82" s="2" t="s">
-        <v>181</v>
-      </c>
       <c r="F82" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G82" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H82" s="2" t="s">
         <v>15</v>
@@ -5167,19 +5161,19 @@
         <v>13</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D83" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="E83" s="2" t="s">
-        <v>183</v>
-      </c>
       <c r="F83" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G83" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H83" s="2" t="s">
         <v>15</v>
@@ -5202,16 +5196,16 @@
         <v>17</v>
       </c>
       <c r="D84" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E84" s="2" t="s">
-        <v>185</v>
-      </c>
       <c r="F84" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G84" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H84" s="2" t="s">
         <v>15</v>
@@ -5234,16 +5228,16 @@
         <v>17</v>
       </c>
       <c r="D85" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="E85" s="2" t="s">
-        <v>187</v>
-      </c>
       <c r="F85" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G85" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H85" s="2" t="s">
         <v>15</v>
@@ -5263,19 +5257,19 @@
         <v>13</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D86" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="E86" s="2" t="s">
-        <v>189</v>
-      </c>
       <c r="F86" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G86" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H86" s="2" t="s">
         <v>15</v>
@@ -5295,19 +5289,19 @@
         <v>7</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D87" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="E87" s="2" t="s">
-        <v>191</v>
-      </c>
       <c r="F87" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>15</v>
@@ -5330,16 +5324,16 @@
         <v>17</v>
       </c>
       <c r="D88" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E88" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E88" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="F88" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G88" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H88" s="2" t="s">
         <v>15</v>
@@ -5359,19 +5353,19 @@
         <v>7</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D89" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="E89" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="E89" s="2" t="s">
-        <v>195</v>
-      </c>
       <c r="F89" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G89" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H89" s="2" t="s">
         <v>15</v>
@@ -5391,19 +5385,19 @@
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D90" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="E90" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="F90" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G90" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H90" s="2" t="s">
         <v>15</v>
@@ -5423,19 +5417,19 @@
         <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D91" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>198</v>
       </c>
-      <c r="E91" s="2" t="s">
-        <v>199</v>
-      </c>
       <c r="F91" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H91" s="2" t="s">
         <v>15</v>
@@ -5455,19 +5449,19 @@
         <v>5</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D92" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E92" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="E92" s="2" t="s">
-        <v>201</v>
-      </c>
       <c r="F92" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G92" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H92" s="2" t="s">
         <v>15</v>
@@ -5487,19 +5481,19 @@
         <v>13</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D93" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>202</v>
       </c>
-      <c r="E93" s="2" t="s">
-        <v>203</v>
-      </c>
       <c r="F93" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G93" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H93" s="2" t="s">
         <v>15</v>
@@ -5519,19 +5513,19 @@
         <v>5</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D94" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>204</v>
       </c>
-      <c r="E94" s="2" t="s">
-        <v>205</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G94" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H94" s="2" t="s">
         <v>15</v>
@@ -5551,19 +5545,19 @@
         <v>7</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D95" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="E95" s="2" t="s">
-        <v>207</v>
-      </c>
       <c r="F95" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G95" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H95" s="2" t="s">
         <v>15</v>
@@ -5583,19 +5577,19 @@
         <v>16</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D96" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="E96" s="2" t="s">
-        <v>209</v>
-      </c>
       <c r="F96" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G96" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H96" s="2" t="s">
         <v>15</v>
@@ -5615,19 +5609,19 @@
         <v>7</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D97" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="E97" s="2" t="s">
-        <v>211</v>
-      </c>
       <c r="F97" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G97" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H97" s="2" t="s">
         <v>15</v>
@@ -5647,19 +5641,19 @@
         <v>13</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D98" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="E98" s="2" t="s">
-        <v>213</v>
-      </c>
       <c r="F98" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G98" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H98" s="2" t="s">
         <v>15</v>
@@ -5679,19 +5673,19 @@
         <v>16</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D99" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="E99" s="2" t="s">
-        <v>215</v>
-      </c>
       <c r="F99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H99" s="2" t="s">
         <v>15</v>
@@ -5711,19 +5705,19 @@
         <v>5</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D100" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="E100" s="2" t="s">
-        <v>217</v>
-      </c>
       <c r="F100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H100" s="2" t="s">
         <v>15</v>
@@ -5743,19 +5737,19 @@
         <v>5</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D101" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="E101" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F101" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H101" s="2" t="s">
         <v>15</v>
@@ -5775,19 +5769,19 @@
         <v>13</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D102" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>220</v>
       </c>
-      <c r="E102" s="2" t="s">
-        <v>221</v>
-      </c>
       <c r="F102" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G102" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H102" s="2" t="s">
         <v>15</v>
@@ -5810,16 +5804,16 @@
         <v>17</v>
       </c>
       <c r="D103" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>222</v>
       </c>
-      <c r="E103" s="2" t="s">
-        <v>223</v>
-      </c>
       <c r="F103" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H103" s="2" t="s">
         <v>15</v>
@@ -5839,19 +5833,19 @@
         <v>13</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D104" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E104" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="E104" s="2" t="s">
-        <v>225</v>
-      </c>
       <c r="F104" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G104" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H104" s="2" t="s">
         <v>15</v>
@@ -5874,16 +5868,16 @@
         <v>17</v>
       </c>
       <c r="D105" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="E105" s="2" t="s">
         <v>226</v>
       </c>
-      <c r="E105" s="2" t="s">
-        <v>227</v>
-      </c>
       <c r="F105" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H105" s="2" t="s">
         <v>15</v>
@@ -5903,25 +5897,25 @@
         <v>7</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D106" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E106" s="2" t="s">
         <v>228</v>
       </c>
-      <c r="E106" s="2" t="s">
-        <v>229</v>
-      </c>
       <c r="F106" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G106" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H106" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I106" s="2" t="n">
-        <v>74.14</v>
+        <v>74.15</v>
       </c>
       <c r="J106" s="2" t="s">
         <v>15</v>
@@ -5935,19 +5929,19 @@
         <v>5</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D107" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E107" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="E107" s="2" t="s">
-        <v>231</v>
-      </c>
       <c r="F107" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H107" s="2" t="s">
         <v>15</v>
@@ -5967,19 +5961,19 @@
         <v>5</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D108" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="E108" s="2" t="s">
         <v>232</v>
       </c>
-      <c r="E108" s="2" t="s">
-        <v>233</v>
-      </c>
       <c r="F108" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G108" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H108" s="2" t="s">
         <v>15</v>
@@ -5999,19 +5993,19 @@
         <v>13</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D109" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E109" s="2" t="s">
         <v>234</v>
       </c>
-      <c r="E109" s="2" t="s">
-        <v>235</v>
-      </c>
       <c r="F109" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H109" s="2" t="s">
         <v>15</v>
@@ -6034,16 +6028,16 @@
         <v>17</v>
       </c>
       <c r="D110" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E110" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="E110" s="2" t="s">
-        <v>237</v>
-      </c>
       <c r="F110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H110" s="2" t="s">
         <v>15</v>
@@ -6063,19 +6057,19 @@
         <v>7</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D111" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="E111" s="2" t="s">
         <v>238</v>
       </c>
-      <c r="E111" s="2" t="s">
-        <v>239</v>
-      </c>
       <c r="F111" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H111" s="2" t="s">
         <v>15</v>
@@ -6095,19 +6089,19 @@
         <v>13</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D112" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E112" s="2" t="s">
         <v>240</v>
       </c>
-      <c r="E112" s="2" t="s">
-        <v>241</v>
-      </c>
       <c r="F112" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G112" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H112" s="2" t="s">
         <v>15</v>
@@ -6127,19 +6121,19 @@
         <v>5</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E113" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="E113" s="2" t="s">
-        <v>243</v>
-      </c>
       <c r="F113" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H113" s="2" t="s">
         <v>15</v>
@@ -6159,19 +6153,19 @@
         <v>5</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D114" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E114" s="2" t="s">
         <v>244</v>
       </c>
-      <c r="E114" s="2" t="s">
-        <v>245</v>
-      </c>
       <c r="F114" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G114" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H114" s="2" t="s">
         <v>15</v>
@@ -6191,19 +6185,19 @@
         <v>7</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D115" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E115" s="2" t="s">
         <v>246</v>
       </c>
-      <c r="E115" s="2" t="s">
-        <v>247</v>
-      </c>
       <c r="F115" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G115" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H115" s="2" t="s">
         <v>15</v>
@@ -6223,19 +6217,19 @@
         <v>16</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D116" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E116" s="2" t="s">
         <v>248</v>
       </c>
-      <c r="E116" s="2" t="s">
-        <v>249</v>
-      </c>
       <c r="F116" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G116" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H116" s="2" t="s">
         <v>15</v>
@@ -6255,19 +6249,19 @@
         <v>5</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D117" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E117" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="E117" s="2" t="s">
-        <v>251</v>
-      </c>
       <c r="F117" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G117" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H117" s="2" t="s">
         <v>15</v>
@@ -6287,19 +6281,19 @@
         <v>16</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D118" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E118" s="2" t="s">
         <v>252</v>
       </c>
-      <c r="E118" s="2" t="s">
-        <v>253</v>
-      </c>
       <c r="F118" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G118" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H118" s="2" t="s">
         <v>15</v>
@@ -6319,19 +6313,19 @@
         <v>13</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D119" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E119" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="E119" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="F119" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G119" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H119" s="2" t="s">
         <v>15</v>
@@ -6351,19 +6345,19 @@
         <v>13</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D120" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E120" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="E120" s="2" t="s">
-        <v>257</v>
-      </c>
       <c r="F120" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G120" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H120" s="2" t="s">
         <v>15</v>
@@ -6383,19 +6377,19 @@
         <v>16</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D121" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E121" s="2" t="s">
         <v>258</v>
       </c>
-      <c r="E121" s="2" t="s">
-        <v>259</v>
-      </c>
       <c r="F121" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G121" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H121" s="2" t="s">
         <v>15</v>
@@ -6415,19 +6409,19 @@
         <v>13</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D122" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E122" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="E122" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="F122" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G122" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H122" s="2" t="s">
         <v>15</v>
@@ -6447,19 +6441,19 @@
         <v>5</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D123" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E123" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="E123" s="2" t="s">
-        <v>263</v>
-      </c>
       <c r="F123" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G123" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H123" s="2" t="s">
         <v>15</v>
@@ -6479,19 +6473,19 @@
         <v>7</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D124" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="E124" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="E124" s="2" t="s">
-        <v>265</v>
-      </c>
       <c r="F124" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G124" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H124" s="2" t="s">
         <v>15</v>
@@ -6514,16 +6508,16 @@
         <v>17</v>
       </c>
       <c r="D125" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E125" s="2" t="s">
         <v>266</v>
       </c>
-      <c r="E125" s="2" t="s">
-        <v>267</v>
-      </c>
       <c r="F125" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G125" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H125" s="2" t="s">
         <v>15</v>
@@ -6543,19 +6537,19 @@
         <v>5</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D126" s="2" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>269</v>
+        <v>57</v>
       </c>
       <c r="F126" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G126" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H126" s="2" t="s">
         <v>15</v>
@@ -6578,16 +6572,16 @@
         <v>17</v>
       </c>
       <c r="D127" s="2" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="F127" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G127" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H127" s="2" t="s">
         <v>15</v>
@@ -6607,19 +6601,19 @@
         <v>13</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D128" s="2" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="F128" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G128" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H128" s="2" t="s">
         <v>15</v>
@@ -6639,19 +6633,19 @@
         <v>7</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D129" s="2" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="F129" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G129" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H129" s="2" t="s">
         <v>15</v>
@@ -6671,19 +6665,19 @@
         <v>16</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D130" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F130" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G130" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H130" s="2" t="s">
         <v>15</v>
@@ -6703,19 +6697,19 @@
         <v>13</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D131" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="F131" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G131" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H131" s="2" t="s">
         <v>15</v>
@@ -6735,19 +6729,19 @@
         <v>13</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D132" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="F132" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G132" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H132" s="2" t="s">
         <v>15</v>
@@ -6767,19 +6761,19 @@
         <v>16</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D133" s="2" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F133" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G133" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H133" s="2" t="s">
         <v>15</v>
@@ -6799,19 +6793,19 @@
         <v>13</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D134" s="2" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="F134" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G134" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H134" s="2" t="s">
         <v>15</v>
@@ -6834,16 +6828,16 @@
         <v>17</v>
       </c>
       <c r="D135" s="2" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="F135" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G135" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H135" s="2" t="s">
         <v>15</v>
@@ -6863,19 +6857,19 @@
         <v>13</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D136" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F136" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G136" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H136" s="2" t="s">
         <v>15</v>
@@ -6895,19 +6889,19 @@
         <v>7</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D137" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="F137" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G137" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H137" s="2" t="s">
         <v>15</v>
@@ -6927,19 +6921,19 @@
         <v>13</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D138" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="F138" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G138" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H138" s="2" t="s">
         <v>15</v>
@@ -6962,16 +6956,16 @@
         <v>17</v>
       </c>
       <c r="D139" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="F139" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G139" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H139" s="2" t="s">
         <v>15</v>
@@ -6994,16 +6988,16 @@
         <v>17</v>
       </c>
       <c r="D140" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="F140" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G140" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H140" s="2" t="s">
         <v>15</v>
@@ -7023,19 +7017,19 @@
         <v>7</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D141" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="F141" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G141" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H141" s="2" t="s">
         <v>15</v>
@@ -7055,19 +7049,19 @@
         <v>16</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D142" s="2" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="F142" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G142" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H142" s="2" t="s">
         <v>15</v>
@@ -7090,16 +7084,16 @@
         <v>17</v>
       </c>
       <c r="D143" s="2" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="F143" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G143" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H143" s="2" t="s">
         <v>15</v>
@@ -7119,19 +7113,19 @@
         <v>13</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D144" s="2" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="F144" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G144" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H144" s="2" t="s">
         <v>15</v>
@@ -7154,16 +7148,16 @@
         <v>17</v>
       </c>
       <c r="D145" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="F145" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G145" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H145" s="2" t="s">
         <v>15</v>
@@ -7183,19 +7177,19 @@
         <v>5</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D146" s="2" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="F146" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G146" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H146" s="2" t="s">
         <v>15</v>
@@ -7215,19 +7209,19 @@
         <v>13</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D147" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F147" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G147" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H147" s="2" t="s">
         <v>15</v>
@@ -7250,16 +7244,16 @@
         <v>17</v>
       </c>
       <c r="D148" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F148" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G148" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H148" s="2" t="s">
         <v>15</v>
@@ -7279,19 +7273,19 @@
         <v>16</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D149" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="F149" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G149" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H149" s="2" t="s">
         <v>15</v>
@@ -7314,16 +7308,16 @@
         <v>17</v>
       </c>
       <c r="D150" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F150" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G150" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H150" s="2" t="s">
         <v>15</v>
@@ -7343,19 +7337,19 @@
         <v>16</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D151" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="F151" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G151" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H151" s="2" t="s">
         <v>15</v>
@@ -7378,16 +7372,16 @@
         <v>17</v>
       </c>
       <c r="D152" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F152" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G152" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H152" s="2" t="s">
         <v>15</v>
@@ -7407,19 +7401,19 @@
         <v>16</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D153" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="F153" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G153" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H153" s="2" t="s">
         <v>15</v>
@@ -7439,19 +7433,19 @@
         <v>13</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D154" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="F154" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G154" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H154" s="2" t="s">
         <v>15</v>
@@ -7471,19 +7465,19 @@
         <v>13</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D155" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="F155" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G155" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H155" s="2" t="s">
         <v>15</v>
@@ -7503,19 +7497,19 @@
         <v>16</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D156" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G156" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H156" s="2" t="s">
         <v>15</v>
@@ -7535,19 +7529,19 @@
         <v>7</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D157" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G157" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H157" s="2" t="s">
         <v>15</v>
@@ -7567,19 +7561,19 @@
         <v>13</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D158" s="2" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G158" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H158" s="2" t="s">
         <v>15</v>
@@ -7599,19 +7593,19 @@
         <v>13</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D159" s="2" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G159" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H159" s="2" t="s">
         <v>15</v>
@@ -7631,19 +7625,19 @@
         <v>7</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D160" s="2" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G160" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H160" s="2" t="s">
         <v>15</v>
@@ -7663,19 +7657,19 @@
         <v>13</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D161" s="2" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G161" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H161" s="2" t="s">
         <v>15</v>
@@ -7695,19 +7689,19 @@
         <v>13</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D162" s="2" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G162" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H162" s="2" t="s">
         <v>15</v>
@@ -7727,19 +7721,19 @@
         <v>13</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D163" s="2" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="E163" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G163" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H163" s="2" t="s">
         <v>15</v>
@@ -7759,19 +7753,19 @@
         <v>7</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D164" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G164" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H164" s="2" t="s">
         <v>15</v>
@@ -7791,19 +7785,19 @@
         <v>5</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D165" s="2" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G165" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H165" s="2" t="s">
         <v>15</v>
@@ -7826,16 +7820,16 @@
         <v>17</v>
       </c>
       <c r="D166" s="2" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G166" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H166" s="2" t="s">
         <v>15</v>
@@ -7855,19 +7849,19 @@
         <v>5</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D167" s="2" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G167" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H167" s="2" t="s">
         <v>15</v>
@@ -7887,19 +7881,19 @@
         <v>13</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D168" s="2" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G168" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H168" s="2" t="s">
         <v>15</v>
@@ -7919,19 +7913,19 @@
         <v>5</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D169" s="2" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G169" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H169" s="2" t="s">
         <v>15</v>
@@ -7951,19 +7945,19 @@
         <v>13</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D170" s="2" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G170" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H170" s="2" t="s">
         <v>15</v>
@@ -7986,16 +7980,16 @@
         <v>17</v>
       </c>
       <c r="D171" s="2" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G171" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H171" s="2" t="s">
         <v>15</v>
@@ -8015,19 +8009,19 @@
         <v>13</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D172" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G172" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H172" s="2" t="s">
         <v>15</v>
@@ -8050,16 +8044,16 @@
         <v>17</v>
       </c>
       <c r="D173" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G173" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H173" s="2" t="s">
         <v>15</v>
@@ -8079,19 +8073,19 @@
         <v>13</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D174" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G174" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H174" s="2" t="s">
         <v>15</v>
@@ -8111,19 +8105,19 @@
         <v>13</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D175" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G175" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H175" s="2" t="s">
         <v>15</v>
@@ -8143,19 +8137,19 @@
         <v>5</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D176" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G176" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H176" s="2" t="s">
         <v>15</v>
@@ -8175,19 +8169,19 @@
         <v>13</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D177" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G177" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H177" s="2" t="s">
         <v>15</v>
@@ -8207,19 +8201,19 @@
         <v>13</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D178" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="E178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G178" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H178" s="2" t="s">
         <v>15</v>
@@ -8242,16 +8236,16 @@
         <v>17</v>
       </c>
       <c r="D179" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="E179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G179" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H179" s="2" t="s">
         <v>15</v>
@@ -8271,19 +8265,19 @@
         <v>13</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D180" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="E180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G180" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H180" s="2" t="s">
         <v>15</v>
@@ -8303,19 +8297,19 @@
         <v>5</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D181" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="E181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G181" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H181" s="2" t="s">
         <v>15</v>
@@ -8338,16 +8332,16 @@
         <v>17</v>
       </c>
       <c r="D182" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="E182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G182" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H182" s="2" t="s">
         <v>15</v>
@@ -8367,19 +8361,19 @@
         <v>13</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D183" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="E183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G183" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H183" s="2" t="s">
         <v>15</v>
@@ -8399,19 +8393,19 @@
         <v>13</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D184" s="2" t="s">
-        <v>384</v>
+        <v>382</v>
       </c>
       <c r="E184" s="2" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G184" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H184" s="2" t="s">
         <v>15</v>
@@ -8431,19 +8425,19 @@
         <v>13</v>
       </c>
       <c r="C185" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D185" s="2" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="E185" s="2" t="s">
-        <v>387</v>
+        <v>385</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G185" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H185" s="2" t="s">
         <v>15</v>
@@ -8463,19 +8457,19 @@
         <v>13</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D186" s="2" t="s">
-        <v>388</v>
+        <v>386</v>
       </c>
       <c r="E186" s="2" t="s">
-        <v>389</v>
+        <v>387</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G186" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="H186" s="2" t="s">
         <v>15</v>
@@ -8495,19 +8489,19 @@
         <v>15</v>
       </c>
       <c r="C187" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D187" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E187" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D187" s="2" t="s">
+      <c r="F187" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="E187" s="2" t="s">
+      <c r="G187" s="2" t="s">
         <v>392</v>
-      </c>
-      <c r="F187" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="G187" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="H187" s="2" t="s">
         <v>15</v>
@@ -8527,19 +8521,19 @@
         <v>3</v>
       </c>
       <c r="C188" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D188" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E188" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D188" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E188" s="2" t="s">
-        <v>397</v>
-      </c>
       <c r="F188" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G188" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H188" s="2" t="s">
         <v>15</v>
@@ -8559,19 +8553,19 @@
         <v>4</v>
       </c>
       <c r="C189" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="D189" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E189" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D189" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E189" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="F189" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G189" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H189" s="2" t="s">
         <v>15</v>
@@ -8591,19 +8585,19 @@
         <v>4</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D190" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="E190" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G190" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H190" s="2" t="s">
         <v>15</v>
@@ -8623,19 +8617,19 @@
         <v>3</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D191" s="2" t="s">
-        <v>403</v>
+        <v>401</v>
       </c>
       <c r="E191" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G191" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H191" s="2" t="s">
         <v>15</v>
@@ -8655,19 +8649,19 @@
         <v>4</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D192" s="2" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="E192" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G192" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H192" s="2" t="s">
         <v>15</v>
@@ -8687,19 +8681,19 @@
         <v>4</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D193" s="2" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
       <c r="E193" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G193" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H193" s="2" t="s">
         <v>15</v>
@@ -8719,19 +8713,19 @@
         <v>3</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D194" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="E194" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G194" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H194" s="2" t="s">
         <v>15</v>
@@ -8751,19 +8745,19 @@
         <v>15</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>390</v>
+        <v>388</v>
       </c>
       <c r="D195" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="E195" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G195" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H195" s="2" t="s">
         <v>15</v>
@@ -8783,19 +8777,19 @@
         <v>4</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D196" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="E196" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G196" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H196" s="2" t="s">
         <v>15</v>
@@ -8815,19 +8809,19 @@
         <v>3</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D197" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="E197" s="2" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G197" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H197" s="2" t="s">
         <v>15</v>
@@ -8847,19 +8841,19 @@
         <v>3</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D198" s="2" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
       <c r="E198" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G198" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H198" s="2" t="s">
         <v>15</v>
@@ -8879,19 +8873,19 @@
         <v>3</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D199" s="2" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
       <c r="E199" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G199" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H199" s="2" t="s">
         <v>15</v>
@@ -8911,19 +8905,19 @@
         <v>2</v>
       </c>
       <c r="C200" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D200" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E200" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D200" s="2" t="s">
-        <v>421</v>
-      </c>
-      <c r="E200" s="2" t="s">
-        <v>422</v>
-      </c>
       <c r="F200" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G200" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H200" s="2" t="s">
         <v>15</v>
@@ -8943,19 +8937,19 @@
         <v>3</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D201" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="E201" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G201" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H201" s="2" t="s">
         <v>15</v>
@@ -8975,19 +8969,19 @@
         <v>4</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D202" s="2" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="E202" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G202" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H202" s="2" t="s">
         <v>15</v>
@@ -9007,19 +9001,19 @@
         <v>3</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D203" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="E203" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G203" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H203" s="2" t="s">
         <v>15</v>
@@ -9039,19 +9033,19 @@
         <v>2</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D204" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="E204" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G204" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H204" s="2" t="s">
         <v>15</v>
@@ -9071,19 +9065,19 @@
         <v>4</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D205" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="E205" s="2" t="s">
-        <v>432</v>
+        <v>430</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G205" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H205" s="2" t="s">
         <v>15</v>
@@ -9103,19 +9097,19 @@
         <v>4</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D206" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E206" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G206" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H206" s="2" t="s">
         <v>15</v>
@@ -9135,19 +9129,19 @@
         <v>1</v>
       </c>
       <c r="C207" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D207" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E207" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D207" s="2" t="s">
-        <v>436</v>
-      </c>
-      <c r="E207" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="F207" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G207" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H207" s="2" t="s">
         <v>15</v>
@@ -9167,19 +9161,19 @@
         <v>4</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D208" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="E208" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G208" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H208" s="2" t="s">
         <v>15</v>
@@ -9199,19 +9193,19 @@
         <v>4</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="E209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G209" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H209" s="2" t="s">
         <v>15</v>
@@ -9231,19 +9225,19 @@
         <v>4</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="E210" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G210" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H210" s="2" t="s">
         <v>15</v>
@@ -9263,19 +9257,19 @@
         <v>4</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D211" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="E211" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="F211" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G211" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H211" s="2" t="s">
         <v>15</v>
@@ -9295,19 +9289,19 @@
         <v>2</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D212" s="2" t="s">
-        <v>446</v>
+        <v>444</v>
       </c>
       <c r="E212" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="F212" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G212" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H212" s="2" t="s">
         <v>15</v>
@@ -9327,19 +9321,19 @@
         <v>1</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D213" s="2" t="s">
-        <v>447</v>
+        <v>445</v>
       </c>
       <c r="E213" s="2" t="s">
-        <v>448</v>
+        <v>446</v>
       </c>
       <c r="F213" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G213" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H213" s="2" t="s">
         <v>15</v>
@@ -9359,19 +9353,19 @@
         <v>4</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D214" s="2" t="s">
-        <v>449</v>
+        <v>447</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>450</v>
+        <v>448</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G214" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H214" s="2" t="s">
         <v>15</v>
@@ -9391,19 +9385,19 @@
         <v>2</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D215" s="2" t="s">
-        <v>451</v>
+        <v>449</v>
       </c>
       <c r="E215" s="2" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G215" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H215" s="2" t="s">
         <v>15</v>
@@ -9423,19 +9417,19 @@
         <v>4</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D216" s="2" t="s">
-        <v>453</v>
+        <v>451</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>454</v>
+        <v>452</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G216" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H216" s="2" t="s">
         <v>15</v>
@@ -9455,19 +9449,19 @@
         <v>2</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>456</v>
+        <v>454</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G217" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H217" s="2" t="s">
         <v>15</v>
@@ -9487,19 +9481,19 @@
         <v>1</v>
       </c>
       <c r="C218" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D218" s="2" t="s">
-        <v>457</v>
+        <v>455</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>458</v>
+        <v>456</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G218" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H218" s="2" t="s">
         <v>15</v>
@@ -9519,19 +9513,19 @@
         <v>4</v>
       </c>
       <c r="C219" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>459</v>
+        <v>457</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>460</v>
+        <v>458</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G219" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H219" s="2" t="s">
         <v>15</v>
@@ -9551,19 +9545,19 @@
         <v>3</v>
       </c>
       <c r="C220" s="2" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
       <c r="D220" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="E220" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G220" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H220" s="2" t="s">
         <v>15</v>
@@ -9583,19 +9577,19 @@
         <v>2</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>463</v>
+        <v>461</v>
       </c>
       <c r="E221" s="2" t="s">
-        <v>464</v>
+        <v>462</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G221" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H221" s="2" t="s">
         <v>15</v>
@@ -9615,19 +9609,19 @@
         <v>1</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>465</v>
+        <v>463</v>
       </c>
       <c r="E222" s="2" t="s">
-        <v>466</v>
+        <v>464</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G222" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H222" s="2" t="s">
         <v>15</v>
@@ -9647,19 +9641,19 @@
         <v>1</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D223" s="2" t="s">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="E223" s="2" t="s">
-        <v>468</v>
+        <v>466</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G223" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H223" s="2" t="s">
         <v>15</v>
@@ -9679,19 +9673,19 @@
         <v>1</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D224" s="2" t="s">
-        <v>469</v>
+        <v>467</v>
       </c>
       <c r="E224" s="2" t="s">
-        <v>470</v>
+        <v>468</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G224" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H224" s="2" t="s">
         <v>15</v>
@@ -9711,19 +9705,19 @@
         <v>2</v>
       </c>
       <c r="C225" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D225" s="2" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>472</v>
+        <v>470</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G225" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H225" s="2" t="s">
         <v>15</v>
@@ -9743,19 +9737,19 @@
         <v>1</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="D226" s="2" t="s">
-        <v>473</v>
+        <v>471</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>474</v>
+        <v>472</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G226" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H226" s="2" t="s">
         <v>15</v>
@@ -9775,19 +9769,19 @@
         <v>2</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D227" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
       <c r="G227" s="2" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="H227" s="2" t="s">
         <v>15</v>
@@ -9807,19 +9801,19 @@
         <v>8</v>
       </c>
       <c r="C228" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="D228" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E228" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D228" s="2" t="s">
+      <c r="F228" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="E228" s="2" t="s">
+      <c r="G228" s="2" t="s">
         <v>479</v>
-      </c>
-      <c r="F228" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="G228" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="H228" s="2" t="s">
         <v>15</v>
@@ -9839,19 +9833,19 @@
         <v>8</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D229" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G229" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H229" s="2" t="s">
         <v>15</v>
@@ -9871,19 +9865,19 @@
         <v>8</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D230" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="E230" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G230" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H230" s="2" t="s">
         <v>15</v>
@@ -9903,19 +9897,19 @@
         <v>8</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D231" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="E231" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G231" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H231" s="2" t="s">
         <v>15</v>
@@ -9935,19 +9929,19 @@
         <v>10</v>
       </c>
       <c r="C232" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="E232" s="2" t="s">
         <v>488</v>
       </c>
-      <c r="D232" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E232" s="2" t="s">
-        <v>490</v>
-      </c>
       <c r="F232" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G232" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H232" s="2" t="s">
         <v>15</v>
@@ -9967,19 +9961,19 @@
         <v>8</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E233" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G233" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H233" s="2" t="s">
         <v>15</v>
@@ -9999,19 +9993,19 @@
         <v>9</v>
       </c>
       <c r="C234" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E234" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="D234" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E234" s="2" t="s">
-        <v>495</v>
-      </c>
       <c r="F234" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G234" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H234" s="2" t="s">
         <v>15</v>
@@ -10031,19 +10025,19 @@
         <v>8</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E235" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G235" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H235" s="2" t="s">
         <v>15</v>
@@ -10063,19 +10057,19 @@
         <v>14</v>
       </c>
       <c r="C236" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E236" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="D236" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="E236" s="2" t="s">
-        <v>500</v>
-      </c>
       <c r="F236" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G236" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H236" s="2" t="s">
         <v>15</v>
@@ -10095,19 +10089,19 @@
         <v>14</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="E237" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G237" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H237" s="2" t="s">
         <v>15</v>
@@ -10127,19 +10121,19 @@
         <v>10</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D238" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="E238" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="F238" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G238" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H238" s="2" t="s">
         <v>15</v>
@@ -10159,19 +10153,19 @@
         <v>8</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E239" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F239" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G239" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H239" s="2" t="s">
         <v>15</v>
@@ -10191,19 +10185,19 @@
         <v>8</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D240" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="E240" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="F240" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G240" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H240" s="2" t="s">
         <v>15</v>
@@ -10223,19 +10217,19 @@
         <v>10</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="E241" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="F241" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G241" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H241" s="2" t="s">
         <v>15</v>
@@ -10255,19 +10249,19 @@
         <v>8</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D242" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E242" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F242" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G242" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H242" s="2" t="s">
         <v>15</v>
@@ -10287,19 +10281,19 @@
         <v>8</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D243" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="E243" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="F243" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G243" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H243" s="2" t="s">
         <v>15</v>
@@ -10319,19 +10313,19 @@
         <v>8</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D244" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="E244" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="F244" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G244" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H244" s="2" t="s">
         <v>15</v>
@@ -10351,19 +10345,19 @@
         <v>8</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D245" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E245" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F245" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G245" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H245" s="2" t="s">
         <v>15</v>
@@ -10383,19 +10377,19 @@
         <v>8</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D246" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="E246" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="F246" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G246" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H246" s="2" t="s">
         <v>15</v>
@@ -10415,19 +10409,19 @@
         <v>10</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D247" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="E247" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="F247" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G247" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H247" s="2" t="s">
         <v>15</v>
@@ -10447,19 +10441,19 @@
         <v>8</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D248" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E248" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F248" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G248" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H248" s="2" t="s">
         <v>15</v>
@@ -10479,19 +10473,19 @@
         <v>9</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D249" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="E249" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="F249" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G249" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H249" s="2" t="s">
         <v>15</v>
@@ -10511,19 +10505,19 @@
         <v>9</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D250" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="E250" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="F250" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G250" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H250" s="2" t="s">
         <v>15</v>
@@ -10543,19 +10537,19 @@
         <v>10</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E251" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G251" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H251" s="2" t="s">
         <v>15</v>
@@ -10575,19 +10569,19 @@
         <v>8</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D252" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="E252" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G252" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H252" s="2" t="s">
         <v>15</v>
@@ -10607,19 +10601,19 @@
         <v>9</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="E253" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G253" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H253" s="2" t="s">
         <v>15</v>
@@ -10639,19 +10633,19 @@
         <v>9</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D254" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E254" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G254" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H254" s="2" t="s">
         <v>15</v>
@@ -10671,19 +10665,19 @@
         <v>14</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D255" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="E255" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G255" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H255" s="2" t="s">
         <v>15</v>
@@ -10703,19 +10697,19 @@
         <v>8</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D256" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G256" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H256" s="2" t="s">
         <v>15</v>
@@ -10735,19 +10729,19 @@
         <v>14</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D257" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E257" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G257" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H257" s="2" t="s">
         <v>15</v>
@@ -10767,19 +10761,19 @@
         <v>9</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D258" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="E258" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G258" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H258" s="2" t="s">
         <v>15</v>
@@ -10799,19 +10793,19 @@
         <v>14</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D259" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="E259" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G259" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H259" s="2" t="s">
         <v>15</v>
@@ -10831,19 +10825,19 @@
         <v>10</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D260" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E260" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G260" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H260" s="2" t="s">
         <v>15</v>
@@ -10863,19 +10857,19 @@
         <v>14</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D261" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="E261" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G261" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H261" s="2" t="s">
         <v>15</v>
@@ -10895,19 +10889,19 @@
         <v>8</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D262" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="E262" s="2" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G262" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H262" s="2" t="s">
         <v>15</v>
@@ -10927,19 +10921,19 @@
         <v>9</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D263" s="2" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="E263" s="2" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G263" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H263" s="2" t="s">
         <v>15</v>
@@ -10959,19 +10953,19 @@
         <v>8</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D264" s="2" t="s">
-        <v>555</v>
+        <v>553</v>
       </c>
       <c r="E264" s="2" t="s">
-        <v>556</v>
+        <v>554</v>
       </c>
       <c r="F264" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G264" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H264" s="2" t="s">
         <v>15</v>
@@ -10991,19 +10985,19 @@
         <v>8</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="E265" s="2" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="F265" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G265" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H265" s="2" t="s">
         <v>15</v>
@@ -11023,19 +11017,19 @@
         <v>9</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D266" s="2" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="E266" s="2" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="F266" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G266" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H266" s="2" t="s">
         <v>15</v>
@@ -11055,19 +11049,19 @@
         <v>8</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D267" s="2" t="s">
-        <v>561</v>
+        <v>559</v>
       </c>
       <c r="E267" s="2" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
       <c r="F267" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G267" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H267" s="2" t="s">
         <v>15</v>
@@ -11087,19 +11081,19 @@
         <v>14</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D268" s="2" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
       <c r="E268" s="2" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="F268" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G268" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H268" s="2" t="s">
         <v>15</v>
@@ -11119,19 +11113,19 @@
         <v>9</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
       <c r="E269" s="2" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G269" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H269" s="2" t="s">
         <v>15</v>
@@ -11151,19 +11145,19 @@
         <v>8</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D270" s="2" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="E270" s="2" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G270" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H270" s="2" t="s">
         <v>15</v>
@@ -11183,19 +11177,19 @@
         <v>14</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>569</v>
+        <v>567</v>
       </c>
       <c r="E271" s="2" t="s">
-        <v>570</v>
+        <v>568</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G271" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H271" s="2" t="s">
         <v>15</v>
@@ -11215,19 +11209,19 @@
         <v>9</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D272" s="2" t="s">
-        <v>571</v>
+        <v>569</v>
       </c>
       <c r="E272" s="2" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G272" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H272" s="2" t="s">
         <v>15</v>
@@ -11247,19 +11241,19 @@
         <v>8</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D273" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="E273" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G273" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H273" s="2" t="s">
         <v>15</v>
@@ -11279,19 +11273,19 @@
         <v>10</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D274" s="2" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="E274" s="2" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G274" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H274" s="2" t="s">
         <v>15</v>
@@ -11311,19 +11305,19 @@
         <v>9</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D275" s="2" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
       <c r="E275" s="2" t="s">
-        <v>578</v>
+        <v>576</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G275" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H275" s="2" t="s">
         <v>15</v>
@@ -11343,19 +11337,19 @@
         <v>9</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D276" s="2" t="s">
-        <v>579</v>
+        <v>577</v>
       </c>
       <c r="E276" s="2" t="s">
-        <v>580</v>
+        <v>578</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G276" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H276" s="2" t="s">
         <v>15</v>
@@ -11375,19 +11369,19 @@
         <v>10</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D277" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="E277" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G277" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H277" s="2" t="s">
         <v>15</v>
@@ -11407,19 +11401,19 @@
         <v>9</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D278" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="E278" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G278" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H278" s="2" t="s">
         <v>15</v>
@@ -11439,19 +11433,19 @@
         <v>10</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D279" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="E279" s="2" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G279" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H279" s="2" t="s">
         <v>15</v>
@@ -11471,19 +11465,19 @@
         <v>9</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D280" s="2" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="E280" s="2" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G280" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H280" s="2" t="s">
         <v>15</v>
@@ -11503,19 +11497,19 @@
         <v>10</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D281" s="2" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
       <c r="E281" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G281" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H281" s="2" t="s">
         <v>15</v>
@@ -11535,19 +11529,19 @@
         <v>9</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D282" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="E282" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G282" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H282" s="2" t="s">
         <v>15</v>
@@ -11567,19 +11561,19 @@
         <v>8</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D283" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E283" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G283" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H283" s="2" t="s">
         <v>15</v>
@@ -11599,19 +11593,19 @@
         <v>10</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D284" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="E284" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G284" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H284" s="2" t="s">
         <v>15</v>
@@ -11631,19 +11625,19 @@
         <v>9</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D285" s="2" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E285" s="2" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G285" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H285" s="2" t="s">
         <v>15</v>
@@ -11663,19 +11657,19 @@
         <v>9</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D286" s="2" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="E286" s="2" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G286" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H286" s="2" t="s">
         <v>15</v>
@@ -11695,19 +11689,19 @@
         <v>8</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D287" s="2" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="E287" s="2" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G287" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H287" s="2" t="s">
         <v>15</v>
@@ -11727,19 +11721,19 @@
         <v>10</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D288" s="2" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E288" s="2" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G288" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H288" s="2" t="s">
         <v>15</v>
@@ -11759,19 +11753,19 @@
         <v>14</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D289" s="2" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="E289" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G289" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H289" s="2" t="s">
         <v>15</v>
@@ -11791,19 +11785,19 @@
         <v>9</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D290" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="E290" s="2" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G290" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H290" s="2" t="s">
         <v>15</v>
@@ -11823,19 +11817,19 @@
         <v>8</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D291" s="2" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="E291" s="2" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G291" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H291" s="2" t="s">
         <v>15</v>
@@ -11855,19 +11849,19 @@
         <v>9</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D292" s="2" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
       <c r="E292" s="2" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G292" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H292" s="2" t="s">
         <v>15</v>
@@ -11887,25 +11881,25 @@
         <v>10</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D293" s="2" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="E293" s="2" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G293" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H293" s="2" t="s">
         <v>15</v>
       </c>
       <c r="I293" s="2" t="n">
-        <v>74.14</v>
+        <v>74.15</v>
       </c>
       <c r="J293" s="2" t="s">
         <v>15</v>
@@ -11919,19 +11913,19 @@
         <v>9</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D294" s="2" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="E294" s="2" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G294" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H294" s="2" t="s">
         <v>15</v>
@@ -11951,19 +11945,19 @@
         <v>8</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D295" s="2" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="E295" s="2" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G295" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H295" s="2" t="s">
         <v>15</v>
@@ -11983,19 +11977,19 @@
         <v>8</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D296" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="E296" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G296" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H296" s="2" t="s">
         <v>15</v>
@@ -12015,19 +12009,19 @@
         <v>8</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D297" s="2" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="E297" s="2" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="F297" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G297" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H297" s="2" t="s">
         <v>15</v>
@@ -12047,19 +12041,19 @@
         <v>10</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D298" s="2" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="E298" s="2" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G298" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H298" s="2" t="s">
         <v>15</v>
@@ -12079,19 +12073,19 @@
         <v>9</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D299" s="2" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="E299" s="2" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G299" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H299" s="2" t="s">
         <v>15</v>
@@ -12111,19 +12105,19 @@
         <v>9</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D300" s="2" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="E300" s="2" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G300" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H300" s="2" t="s">
         <v>15</v>
@@ -12143,19 +12137,19 @@
         <v>9</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D301" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="E301" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G301" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H301" s="2" t="s">
         <v>15</v>
@@ -12175,19 +12169,19 @@
         <v>10</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D302" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="E302" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G302" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H302" s="2" t="s">
         <v>15</v>
@@ -12207,19 +12201,19 @@
         <v>10</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D303" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="E303" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G303" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H303" s="2" t="s">
         <v>15</v>
@@ -12239,19 +12233,19 @@
         <v>9</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D304" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="E304" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G304" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H304" s="2" t="s">
         <v>15</v>
@@ -12271,19 +12265,19 @@
         <v>10</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D305" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="E305" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G305" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H305" s="2" t="s">
         <v>15</v>
@@ -12303,19 +12297,19 @@
         <v>9</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D306" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="E306" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G306" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H306" s="2" t="s">
         <v>15</v>
@@ -12335,19 +12329,19 @@
         <v>10</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D307" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="E307" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G307" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H307" s="2" t="s">
         <v>15</v>
@@ -12367,19 +12361,19 @@
         <v>8</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D308" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="E308" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G308" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H308" s="2" t="s">
         <v>15</v>
@@ -12399,19 +12393,19 @@
         <v>10</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D309" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="E309" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G309" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H309" s="2" t="s">
         <v>15</v>
@@ -12431,19 +12425,19 @@
         <v>14</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D310" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="E310" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G310" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H310" s="2" t="s">
         <v>15</v>
@@ -12463,19 +12457,19 @@
         <v>8</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D311" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="E311" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G311" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H311" s="2" t="s">
         <v>15</v>
@@ -12495,19 +12489,19 @@
         <v>14</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D312" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="E312" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G312" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H312" s="2" t="s">
         <v>15</v>
@@ -12527,19 +12521,19 @@
         <v>9</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D313" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="E313" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G313" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H313" s="2" t="s">
         <v>15</v>
@@ -12559,19 +12553,19 @@
         <v>10</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D314" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="E314" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G314" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H314" s="2" t="s">
         <v>15</v>
@@ -12591,19 +12585,19 @@
         <v>9</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D315" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="E315" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="F315" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G315" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H315" s="2" t="s">
         <v>15</v>
@@ -12623,19 +12617,19 @@
         <v>8</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D316" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="E316" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="F316" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G316" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H316" s="2" t="s">
         <v>15</v>
@@ -12655,19 +12649,19 @@
         <v>9</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D317" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="E317" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="F317" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G317" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H317" s="2" t="s">
         <v>15</v>
@@ -12687,19 +12681,19 @@
         <v>10</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D318" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="E318" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="F318" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G318" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H318" s="2" t="s">
         <v>15</v>
@@ -12719,19 +12713,19 @@
         <v>10</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D319" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="E319" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="F319" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G319" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H319" s="2" t="s">
         <v>15</v>
@@ -12751,19 +12745,19 @@
         <v>8</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D320" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="E320" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="F320" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G320" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H320" s="2" t="s">
         <v>15</v>
@@ -12783,19 +12777,19 @@
         <v>14</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="D321" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="E321" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="F321" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G321" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H321" s="2" t="s">
         <v>15</v>
@@ -12815,19 +12809,19 @@
         <v>10</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D322" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="E322" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="F322" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G322" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H322" s="2" t="s">
         <v>15</v>
@@ -12847,19 +12841,19 @@
         <v>10</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D323" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="E323" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="F323" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G323" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H323" s="2" t="s">
         <v>15</v>
@@ -12879,19 +12873,19 @@
         <v>10</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D324" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E324" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="F324" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G324" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H324" s="2" t="s">
         <v>15</v>
@@ -12911,19 +12905,19 @@
         <v>10</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D325" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="E325" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="F325" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G325" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H325" s="2" t="s">
         <v>15</v>
@@ -12943,19 +12937,19 @@
         <v>9</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D326" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="E326" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G326" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H326" s="2" t="s">
         <v>15</v>
@@ -12975,19 +12969,19 @@
         <v>10</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D327" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="E327" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G327" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H327" s="2" t="s">
         <v>15</v>
@@ -13007,19 +13001,19 @@
         <v>10</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D328" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="E328" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G328" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H328" s="2" t="s">
         <v>15</v>
@@ -13039,19 +13033,19 @@
         <v>10</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D329" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="E329" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G329" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H329" s="2" t="s">
         <v>15</v>
@@ -13071,19 +13065,19 @@
         <v>8</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="D330" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="E330" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G330" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H330" s="2" t="s">
         <v>15</v>
@@ -13103,19 +13097,19 @@
         <v>10</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D331" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="E331" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G331" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H331" s="2" t="s">
         <v>15</v>
@@ -13135,19 +13129,19 @@
         <v>9</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D332" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="E332" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G332" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H332" s="2" t="s">
         <v>15</v>
@@ -13167,19 +13161,19 @@
         <v>9</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D333" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="E333" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G333" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H333" s="2" t="s">
         <v>15</v>
@@ -13199,19 +13193,19 @@
         <v>9</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="D334" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="E334" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="G334" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="H334" s="2" t="s">
         <v>15</v>
@@ -13241,7 +13235,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>8</v>
@@ -13249,50 +13243,50 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
     </row>
   </sheetData>
@@ -13314,21 +13308,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="C1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>15</v>
@@ -13337,7 +13331,7 @@
         <v>2020</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
     </row>
   </sheetData>
